--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="563">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1649,6 +1649,57 @@
   </si>
   <si>
     <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>43.8563° N, 18.4131° E</t>
+  </si>
+  <si>
+    <t>Mostar</t>
+  </si>
+  <si>
+    <t>43.3438° N, 17.8078° E</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Dubrovnik</t>
+  </si>
+  <si>
+    <t>42.6507° N, 18.0944° E</t>
+  </si>
+  <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
+    <t>Budva</t>
+  </si>
+  <si>
+    <t>42.2911° N, 18.8403° E</t>
+  </si>
+  <si>
+    <t>Albania</t>
+  </si>
+  <si>
+    <t>Tirana</t>
+  </si>
+  <si>
+    <t>41.3275° N, 19.8187° E</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
+    <t>Ohrid</t>
+  </si>
+  <si>
+    <t>41.1231° N, 20.8016° E</t>
   </si>
 </sst>
 </file>
@@ -2911,7 +2962,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F349"/>
+  <dimension ref="A2:F357"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -9237,6 +9288,150 @@
       </c>
       <c r="F349" s="14"/>
     </row>
+    <row r="350" ht="20.05" customHeight="1">
+      <c r="A350" t="s" s="9">
+        <v>546</v>
+      </c>
+      <c r="B350" t="s" s="9">
+        <v>547</v>
+      </c>
+      <c r="C350" t="s" s="10">
+        <v>548</v>
+      </c>
+      <c r="D350" t="s" s="15">
+        <v>545</v>
+      </c>
+      <c r="E350" s="12">
+        <v>46082</v>
+      </c>
+      <c r="F350" s="14"/>
+    </row>
+    <row r="351" ht="20.05" customHeight="1">
+      <c r="A351" t="s" s="9">
+        <v>546</v>
+      </c>
+      <c r="B351" t="s" s="9">
+        <v>549</v>
+      </c>
+      <c r="C351" t="s" s="10">
+        <v>550</v>
+      </c>
+      <c r="D351" s="11">
+        <v>46082</v>
+      </c>
+      <c r="E351" s="12">
+        <v>46083</v>
+      </c>
+      <c r="F351" s="14"/>
+    </row>
+    <row r="352" ht="20.05" customHeight="1">
+      <c r="A352" t="s" s="9">
+        <v>551</v>
+      </c>
+      <c r="B352" t="s" s="9">
+        <v>552</v>
+      </c>
+      <c r="C352" t="s" s="10">
+        <v>553</v>
+      </c>
+      <c r="D352" s="11">
+        <v>46083</v>
+      </c>
+      <c r="E352" s="12">
+        <v>46085</v>
+      </c>
+      <c r="F352" s="14"/>
+    </row>
+    <row r="353" ht="20.05" customHeight="1">
+      <c r="A353" t="s" s="9">
+        <v>554</v>
+      </c>
+      <c r="B353" t="s" s="9">
+        <v>555</v>
+      </c>
+      <c r="C353" t="s" s="10">
+        <v>556</v>
+      </c>
+      <c r="D353" s="11">
+        <v>46085</v>
+      </c>
+      <c r="E353" s="12">
+        <v>46087</v>
+      </c>
+      <c r="F353" s="14"/>
+    </row>
+    <row r="354" ht="20.05" customHeight="1">
+      <c r="A354" t="s" s="9">
+        <v>557</v>
+      </c>
+      <c r="B354" t="s" s="9">
+        <v>558</v>
+      </c>
+      <c r="C354" t="s" s="10">
+        <v>559</v>
+      </c>
+      <c r="D354" s="11">
+        <v>46087</v>
+      </c>
+      <c r="E354" s="12">
+        <v>46089</v>
+      </c>
+      <c r="F354" s="14"/>
+    </row>
+    <row r="355" ht="20.05" customHeight="1">
+      <c r="A355" t="s" s="9">
+        <v>560</v>
+      </c>
+      <c r="B355" t="s" s="9">
+        <v>561</v>
+      </c>
+      <c r="C355" t="s" s="10">
+        <v>562</v>
+      </c>
+      <c r="D355" s="11">
+        <v>46089</v>
+      </c>
+      <c r="E355" s="12">
+        <v>46089</v>
+      </c>
+      <c r="F355" s="14"/>
+    </row>
+    <row r="356" ht="20.05" customHeight="1">
+      <c r="A356" t="s" s="9">
+        <v>557</v>
+      </c>
+      <c r="B356" t="s" s="9">
+        <v>558</v>
+      </c>
+      <c r="C356" t="s" s="10">
+        <v>559</v>
+      </c>
+      <c r="D356" s="11">
+        <v>46089</v>
+      </c>
+      <c r="E356" s="12">
+        <v>46091</v>
+      </c>
+      <c r="F356" s="14"/>
+    </row>
+    <row r="357" ht="20.05" customHeight="1">
+      <c r="A357" t="s" s="9">
+        <v>292</v>
+      </c>
+      <c r="B357" t="s" s="9">
+        <v>293</v>
+      </c>
+      <c r="C357" t="s" s="10">
+        <v>294</v>
+      </c>
+      <c r="D357" s="11">
+        <v>46091</v>
+      </c>
+      <c r="E357" s="12">
+        <v>46092</v>
+      </c>
+      <c r="F357" s="14"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="566">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1700,6 +1700,15 @@
   </si>
   <si>
     <t>41.1231° N, 20.8016° E</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Budapest</t>
+  </si>
+  <si>
+    <t>47.4979° N, 19.0402° E</t>
   </si>
 </sst>
 </file>
@@ -2962,7 +2971,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F357"/>
+  <dimension ref="A2:F359"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -9428,9 +9437,45 @@
         <v>46091</v>
       </c>
       <c r="E357" s="12">
-        <v>46092</v>
+        <v>46115</v>
       </c>
       <c r="F357" s="14"/>
+    </row>
+    <row r="358" ht="20.05" customHeight="1">
+      <c r="A358" t="s" s="9">
+        <v>563</v>
+      </c>
+      <c r="B358" t="s" s="9">
+        <v>564</v>
+      </c>
+      <c r="C358" t="s" s="10">
+        <v>565</v>
+      </c>
+      <c r="D358" s="11">
+        <v>46115</v>
+      </c>
+      <c r="E358" s="12">
+        <v>46118</v>
+      </c>
+      <c r="F358" s="14"/>
+    </row>
+    <row r="359" ht="20.05" customHeight="1">
+      <c r="A359" t="s" s="9">
+        <v>292</v>
+      </c>
+      <c r="B359" t="s" s="9">
+        <v>293</v>
+      </c>
+      <c r="C359" t="s" s="10">
+        <v>294</v>
+      </c>
+      <c r="D359" s="11">
+        <v>46118</v>
+      </c>
+      <c r="E359" s="12">
+        <v>46119</v>
+      </c>
+      <c r="F359" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="597">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1709,6 +1709,99 @@
   </si>
   <si>
     <t>47.4979° N, 19.0402° E</t>
+  </si>
+  <si>
+    <t>Slovenia</t>
+  </si>
+  <si>
+    <t>Maribor</t>
+  </si>
+  <si>
+    <t>46.5547° N, 15.6459° E</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Czechia</t>
+  </si>
+  <si>
+    <t>Brno</t>
+  </si>
+  <si>
+    <t>49.1951° N, 16.6068° E</t>
+  </si>
+  <si>
+    <t>Varna</t>
+  </si>
+  <si>
+    <t>43.2141° N, 27.9147° E</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Luxembourg City</t>
+  </si>
+  <si>
+    <t>49.8153° N, 6.1296° E</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>Tangier</t>
+  </si>
+  <si>
+    <t>35.7595° N, 5.8340° W</t>
+  </si>
+  <si>
+    <t>Tetouan</t>
+  </si>
+  <si>
+    <t>35.5717° N, 5.3597° W</t>
+  </si>
+  <si>
+    <t>Chefchaouen</t>
+  </si>
+  <si>
+    <t>35.1688° N, 5.2684° W</t>
+  </si>
+  <si>
+    <t>Fes</t>
+  </si>
+  <si>
+    <t>34.0181° N, 5.0078° W</t>
+  </si>
+  <si>
+    <t>Meknes</t>
+  </si>
+  <si>
+    <t>33.8675° N, 5.5382° W</t>
+  </si>
+  <si>
+    <t>Rabat</t>
+  </si>
+  <si>
+    <t>34.0084° N, 6.8539° W</t>
+  </si>
+  <si>
+    <t>Ouarzazate</t>
+  </si>
+  <si>
+    <t>30.9335° N, 6.9370° W</t>
+  </si>
+  <si>
+    <t>Marrakesh</t>
+  </si>
+  <si>
+    <t>31.6225° N, 7.9898° W</t>
+  </si>
+  <si>
+    <t>Casablanca</t>
+  </si>
+  <si>
+    <t>33.5731° N, 7.5898° W</t>
   </si>
 </sst>
 </file>
@@ -2971,7 +3064,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F359"/>
+  <dimension ref="A2:F380"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -9473,9 +9566,417 @@
         <v>46118</v>
       </c>
       <c r="E359" s="12">
-        <v>46119</v>
+        <v>46156</v>
       </c>
       <c r="F359" s="14"/>
+    </row>
+    <row r="360" ht="20.05" customHeight="1">
+      <c r="A360" t="s" s="9">
+        <v>324</v>
+      </c>
+      <c r="B360" t="s" s="9">
+        <v>325</v>
+      </c>
+      <c r="C360" t="s" s="10">
+        <v>326</v>
+      </c>
+      <c r="D360" s="11">
+        <v>46156</v>
+      </c>
+      <c r="E360" s="12">
+        <v>46156</v>
+      </c>
+      <c r="F360" s="14"/>
+    </row>
+    <row r="361" ht="20.05" customHeight="1">
+      <c r="A361" t="s" s="9">
+        <v>566</v>
+      </c>
+      <c r="B361" t="s" s="9">
+        <v>567</v>
+      </c>
+      <c r="C361" t="s" s="10">
+        <v>568</v>
+      </c>
+      <c r="D361" s="11">
+        <v>46156</v>
+      </c>
+      <c r="E361" s="12">
+        <v>46157</v>
+      </c>
+      <c r="F361" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="362" ht="20.05" customHeight="1">
+      <c r="A362" t="s" s="9">
+        <v>324</v>
+      </c>
+      <c r="B362" t="s" s="9">
+        <v>325</v>
+      </c>
+      <c r="C362" t="s" s="10">
+        <v>326</v>
+      </c>
+      <c r="D362" s="11">
+        <v>46157</v>
+      </c>
+      <c r="E362" s="12">
+        <v>46157</v>
+      </c>
+      <c r="F362" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="363" ht="20.05" customHeight="1">
+      <c r="A363" t="s" s="9">
+        <v>570</v>
+      </c>
+      <c r="B363" t="s" s="9">
+        <v>571</v>
+      </c>
+      <c r="C363" t="s" s="10">
+        <v>572</v>
+      </c>
+      <c r="D363" s="11">
+        <v>46157</v>
+      </c>
+      <c r="E363" s="12">
+        <v>46158</v>
+      </c>
+      <c r="F363" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="364" ht="20.05" customHeight="1">
+      <c r="A364" t="s" s="9">
+        <v>324</v>
+      </c>
+      <c r="B364" t="s" s="9">
+        <v>325</v>
+      </c>
+      <c r="C364" t="s" s="10">
+        <v>326</v>
+      </c>
+      <c r="D364" s="11">
+        <v>46158</v>
+      </c>
+      <c r="E364" s="12">
+        <v>46159</v>
+      </c>
+      <c r="F364" s="14"/>
+    </row>
+    <row r="365" ht="20.05" customHeight="1">
+      <c r="A365" t="s" s="9">
+        <v>292</v>
+      </c>
+      <c r="B365" t="s" s="9">
+        <v>293</v>
+      </c>
+      <c r="C365" t="s" s="10">
+        <v>294</v>
+      </c>
+      <c r="D365" s="11">
+        <v>46159</v>
+      </c>
+      <c r="E365" s="12">
+        <v>46172</v>
+      </c>
+      <c r="F365" s="14"/>
+    </row>
+    <row r="366" ht="20.05" customHeight="1">
+      <c r="A366" t="s" s="9">
+        <v>483</v>
+      </c>
+      <c r="B366" t="s" s="9">
+        <v>573</v>
+      </c>
+      <c r="C366" t="s" s="10">
+        <v>574</v>
+      </c>
+      <c r="D366" s="11">
+        <v>46172</v>
+      </c>
+      <c r="E366" s="12">
+        <v>46179</v>
+      </c>
+      <c r="F366" s="14"/>
+    </row>
+    <row r="367" ht="20.05" customHeight="1">
+      <c r="A367" t="s" s="9">
+        <v>292</v>
+      </c>
+      <c r="B367" t="s" s="9">
+        <v>293</v>
+      </c>
+      <c r="C367" t="s" s="10">
+        <v>294</v>
+      </c>
+      <c r="D367" s="11">
+        <v>46179</v>
+      </c>
+      <c r="E367" s="12">
+        <v>46192</v>
+      </c>
+      <c r="F367" s="14"/>
+    </row>
+    <row r="368" ht="20.05" customHeight="1">
+      <c r="A368" t="s" s="9">
+        <v>412</v>
+      </c>
+      <c r="B368" t="s" s="9">
+        <v>458</v>
+      </c>
+      <c r="C368" t="s" s="10">
+        <v>459</v>
+      </c>
+      <c r="D368" s="11">
+        <v>46192</v>
+      </c>
+      <c r="E368" s="12">
+        <v>46193</v>
+      </c>
+      <c r="F368" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="369" ht="20.05" customHeight="1">
+      <c r="A369" t="s" s="9">
+        <v>575</v>
+      </c>
+      <c r="B369" t="s" s="9">
+        <v>576</v>
+      </c>
+      <c r="C369" t="s" s="10">
+        <v>577</v>
+      </c>
+      <c r="D369" s="11">
+        <v>46193</v>
+      </c>
+      <c r="E369" s="12">
+        <v>46193</v>
+      </c>
+      <c r="F369" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="370" ht="20.05" customHeight="1">
+      <c r="A370" t="s" s="9">
+        <v>412</v>
+      </c>
+      <c r="B370" t="s" s="9">
+        <v>458</v>
+      </c>
+      <c r="C370" t="s" s="10">
+        <v>459</v>
+      </c>
+      <c r="D370" s="11">
+        <v>46193</v>
+      </c>
+      <c r="E370" s="12">
+        <v>46194</v>
+      </c>
+      <c r="F370" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="371" ht="20.05" customHeight="1">
+      <c r="A371" t="s" s="9">
+        <v>578</v>
+      </c>
+      <c r="B371" t="s" s="9">
+        <v>579</v>
+      </c>
+      <c r="C371" t="s" s="10">
+        <v>580</v>
+      </c>
+      <c r="D371" s="11">
+        <v>46194</v>
+      </c>
+      <c r="E371" s="12">
+        <v>46196</v>
+      </c>
+      <c r="F371" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="372" ht="20.05" customHeight="1">
+      <c r="A372" t="s" s="9">
+        <v>578</v>
+      </c>
+      <c r="B372" t="s" s="9">
+        <v>581</v>
+      </c>
+      <c r="C372" t="s" s="10">
+        <v>582</v>
+      </c>
+      <c r="D372" s="11">
+        <v>46196</v>
+      </c>
+      <c r="E372" s="12">
+        <v>46197</v>
+      </c>
+      <c r="F372" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="373" ht="20.05" customHeight="1">
+      <c r="A373" t="s" s="9">
+        <v>578</v>
+      </c>
+      <c r="B373" t="s" s="9">
+        <v>583</v>
+      </c>
+      <c r="C373" t="s" s="10">
+        <v>584</v>
+      </c>
+      <c r="D373" s="11">
+        <v>46197</v>
+      </c>
+      <c r="E373" s="12">
+        <v>46198</v>
+      </c>
+      <c r="F373" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="374" ht="20.05" customHeight="1">
+      <c r="A374" t="s" s="9">
+        <v>578</v>
+      </c>
+      <c r="B374" t="s" s="9">
+        <v>585</v>
+      </c>
+      <c r="C374" t="s" s="10">
+        <v>586</v>
+      </c>
+      <c r="D374" s="11">
+        <v>46198</v>
+      </c>
+      <c r="E374" s="12">
+        <v>46199</v>
+      </c>
+      <c r="F374" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="375" ht="20.05" customHeight="1">
+      <c r="A375" t="s" s="9">
+        <v>578</v>
+      </c>
+      <c r="B375" t="s" s="9">
+        <v>587</v>
+      </c>
+      <c r="C375" t="s" s="10">
+        <v>588</v>
+      </c>
+      <c r="D375" s="11">
+        <v>46199</v>
+      </c>
+      <c r="E375" s="12">
+        <v>46200</v>
+      </c>
+      <c r="F375" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="376" ht="20.05" customHeight="1">
+      <c r="A376" t="s" s="9">
+        <v>578</v>
+      </c>
+      <c r="B376" t="s" s="9">
+        <v>589</v>
+      </c>
+      <c r="C376" t="s" s="10">
+        <v>590</v>
+      </c>
+      <c r="D376" s="11">
+        <v>46200</v>
+      </c>
+      <c r="E376" s="12">
+        <v>46203</v>
+      </c>
+      <c r="F376" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="377" ht="20.05" customHeight="1">
+      <c r="A377" t="s" s="9">
+        <v>578</v>
+      </c>
+      <c r="B377" t="s" s="9">
+        <v>591</v>
+      </c>
+      <c r="C377" t="s" s="10">
+        <v>592</v>
+      </c>
+      <c r="D377" s="11">
+        <v>46203</v>
+      </c>
+      <c r="E377" s="12">
+        <v>46205</v>
+      </c>
+      <c r="F377" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="378" ht="20.05" customHeight="1">
+      <c r="A378" t="s" s="9">
+        <v>578</v>
+      </c>
+      <c r="B378" t="s" s="9">
+        <v>593</v>
+      </c>
+      <c r="C378" t="s" s="10">
+        <v>594</v>
+      </c>
+      <c r="D378" s="11">
+        <v>46205</v>
+      </c>
+      <c r="E378" s="12">
+        <v>46208</v>
+      </c>
+      <c r="F378" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="379" ht="20.05" customHeight="1">
+      <c r="A379" t="s" s="9">
+        <v>578</v>
+      </c>
+      <c r="B379" t="s" s="9">
+        <v>595</v>
+      </c>
+      <c r="C379" t="s" s="10">
+        <v>596</v>
+      </c>
+      <c r="D379" s="11">
+        <v>46208</v>
+      </c>
+      <c r="E379" s="12">
+        <v>46221</v>
+      </c>
+      <c r="F379" t="s" s="13">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="380" ht="20.05" customHeight="1">
+      <c r="A380" t="s" s="9">
+        <v>292</v>
+      </c>
+      <c r="B380" t="s" s="9">
+        <v>293</v>
+      </c>
+      <c r="C380" t="s" s="10">
+        <v>294</v>
+      </c>
+      <c r="D380" s="11">
+        <v>46221</v>
+      </c>
+      <c r="E380" s="12">
+        <v>46234</v>
+      </c>
+      <c r="F380" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -5,13 +5,13 @@
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet 1 - trips_verbose_v2" sheetId="1" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="619">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1711,6 +1711,12 @@
     <t>47.4979° N, 19.0402° E</t>
   </si>
   <si>
+    <t>Graz</t>
+  </si>
+  <si>
+    <t>47.0679° N, 15.4417° E</t>
+  </si>
+  <si>
     <t>Slovenia</t>
   </si>
   <si>
@@ -1720,24 +1726,24 @@
     <t>46.5547° N, 15.6459° E</t>
   </si>
   <si>
+    <t>Czechia</t>
+  </si>
+  <si>
+    <t>Brno</t>
+  </si>
+  <si>
+    <t>49.1951° N, 16.6068° E</t>
+  </si>
+  <si>
+    <t>Varna</t>
+  </si>
+  <si>
+    <t>43.2141° N, 27.9147° E</t>
+  </si>
+  <si>
     <t>TBD</t>
   </si>
   <si>
-    <t>Czechia</t>
-  </si>
-  <si>
-    <t>Brno</t>
-  </si>
-  <si>
-    <t>49.1951° N, 16.6068° E</t>
-  </si>
-  <si>
-    <t>Varna</t>
-  </si>
-  <si>
-    <t>43.2141° N, 27.9147° E</t>
-  </si>
-  <si>
     <t>Luxembourg</t>
   </si>
   <si>
@@ -1747,6 +1753,12 @@
     <t>49.8153° N, 6.1296° E</t>
   </si>
   <si>
+    <t>Málaga</t>
+  </si>
+  <si>
+    <t>36.7178° N, 4.4256° W</t>
+  </si>
+  <si>
     <t>Morocco</t>
   </si>
   <si>
@@ -1786,22 +1798,76 @@
     <t>34.0084° N, 6.8539° W</t>
   </si>
   <si>
+    <t>Casablanca</t>
+  </si>
+  <si>
+    <t>33.5731° N, 7.5898° W</t>
+  </si>
+  <si>
     <t>Ouarzazate</t>
   </si>
   <si>
     <t>30.9335° N, 6.9370° W</t>
   </si>
   <si>
+    <t>Aït Benhaddou</t>
+  </si>
+  <si>
+    <t>31.0470° N, 7.1319° W</t>
+  </si>
+  <si>
     <t>Marrakesh</t>
   </si>
   <si>
     <t>31.6225° N, 7.9898° W</t>
   </si>
   <si>
-    <t>Casablanca</t>
-  </si>
-  <si>
-    <t>33.5731° N, 7.5898° W</t>
+    <t>Vietnam</t>
+  </si>
+  <si>
+    <t>Hanoi</t>
+  </si>
+  <si>
+    <t>21.0278° N, 105.8342° E</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh City</t>
+  </si>
+  <si>
+    <t>10.8231° N, 106.6297° E</t>
+  </si>
+  <si>
+    <t>Cambodia</t>
+  </si>
+  <si>
+    <t>Phnom Penh</t>
+  </si>
+  <si>
+    <t>11.5564° N, 104.9282° E</t>
+  </si>
+  <si>
+    <t>Krong Siem Reap</t>
+  </si>
+  <si>
+    <t>13.3633° N, 103.8564° E</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Jakarta</t>
+  </si>
+  <si>
+    <t>6.1944° S, 106.8229° E</t>
+  </si>
+  <si>
+    <t>Oman</t>
+  </si>
+  <si>
+    <t>Muscat</t>
+  </si>
+  <si>
+    <t>23.5880° N, 58.3829° E</t>
   </si>
 </sst>
 </file>
@@ -1963,7 +2029,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2010,6 +2076,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -3064,7 +3139,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F380"/>
+  <dimension ref="A2:F392"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -9590,393 +9665,615 @@
     </row>
     <row r="361" ht="20.05" customHeight="1">
       <c r="A361" t="s" s="9">
+        <v>324</v>
+      </c>
+      <c r="B361" t="s" s="9">
         <v>566</v>
       </c>
-      <c r="B361" t="s" s="9">
+      <c r="C361" t="s" s="10">
         <v>567</v>
-      </c>
-      <c r="C361" t="s" s="10">
-        <v>568</v>
       </c>
       <c r="D361" s="11">
         <v>46156</v>
       </c>
       <c r="E361" s="12">
-        <v>46157</v>
-      </c>
-      <c r="F361" t="s" s="13">
-        <v>569</v>
-      </c>
+        <v>46156</v>
+      </c>
+      <c r="F361" s="14"/>
     </row>
     <row r="362" ht="20.05" customHeight="1">
       <c r="A362" t="s" s="9">
-        <v>324</v>
+        <v>568</v>
       </c>
       <c r="B362" t="s" s="9">
-        <v>325</v>
+        <v>569</v>
       </c>
       <c r="C362" t="s" s="10">
-        <v>326</v>
+        <v>570</v>
       </c>
       <c r="D362" s="11">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="E362" s="12">
         <v>46157</v>
       </c>
-      <c r="F362" t="s" s="13">
-        <v>569</v>
-      </c>
+      <c r="F362" s="14"/>
     </row>
     <row r="363" ht="20.05" customHeight="1">
       <c r="A363" t="s" s="9">
-        <v>570</v>
+        <v>324</v>
       </c>
       <c r="B363" t="s" s="9">
-        <v>571</v>
+        <v>325</v>
       </c>
       <c r="C363" t="s" s="10">
-        <v>572</v>
+        <v>326</v>
       </c>
       <c r="D363" s="11">
         <v>46157</v>
       </c>
       <c r="E363" s="12">
-        <v>46158</v>
-      </c>
-      <c r="F363" t="s" s="13">
-        <v>569</v>
-      </c>
+        <v>46157</v>
+      </c>
+      <c r="F363" s="14"/>
     </row>
     <row r="364" ht="20.05" customHeight="1">
       <c r="A364" t="s" s="9">
-        <v>324</v>
+        <v>571</v>
       </c>
       <c r="B364" t="s" s="9">
-        <v>325</v>
+        <v>572</v>
       </c>
       <c r="C364" t="s" s="10">
-        <v>326</v>
+        <v>573</v>
       </c>
       <c r="D364" s="11">
+        <v>46157</v>
+      </c>
+      <c r="E364" s="12">
         <v>46158</v>
-      </c>
-      <c r="E364" s="12">
-        <v>46159</v>
       </c>
       <c r="F364" s="14"/>
     </row>
     <row r="365" ht="20.05" customHeight="1">
       <c r="A365" t="s" s="9">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="B365" t="s" s="9">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="C365" t="s" s="10">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="D365" s="11">
+        <v>46158</v>
+      </c>
+      <c r="E365" s="12">
         <v>46159</v>
-      </c>
-      <c r="E365" s="12">
-        <v>46172</v>
       </c>
       <c r="F365" s="14"/>
     </row>
     <row r="366" ht="20.05" customHeight="1">
       <c r="A366" t="s" s="9">
-        <v>483</v>
+        <v>292</v>
       </c>
       <c r="B366" t="s" s="9">
-        <v>573</v>
+        <v>293</v>
       </c>
       <c r="C366" t="s" s="10">
-        <v>574</v>
+        <v>294</v>
       </c>
       <c r="D366" s="11">
+        <v>46159</v>
+      </c>
+      <c r="E366" s="12">
         <v>46172</v>
-      </c>
-      <c r="E366" s="12">
-        <v>46179</v>
       </c>
       <c r="F366" s="14"/>
     </row>
     <row r="367" ht="20.05" customHeight="1">
       <c r="A367" t="s" s="9">
-        <v>292</v>
+        <v>483</v>
       </c>
       <c r="B367" t="s" s="9">
-        <v>293</v>
+        <v>574</v>
       </c>
       <c r="C367" t="s" s="10">
-        <v>294</v>
+        <v>575</v>
       </c>
       <c r="D367" s="11">
+        <v>46172</v>
+      </c>
+      <c r="E367" s="12">
         <v>46179</v>
-      </c>
-      <c r="E367" s="12">
-        <v>46192</v>
       </c>
       <c r="F367" s="14"/>
     </row>
     <row r="368" ht="20.05" customHeight="1">
       <c r="A368" t="s" s="9">
-        <v>412</v>
+        <v>292</v>
       </c>
       <c r="B368" t="s" s="9">
-        <v>458</v>
+        <v>293</v>
       </c>
       <c r="C368" t="s" s="10">
-        <v>459</v>
+        <v>294</v>
       </c>
       <c r="D368" s="11">
+        <v>46179</v>
+      </c>
+      <c r="E368" s="12">
         <v>46192</v>
       </c>
-      <c r="E368" s="12">
-        <v>46193</v>
-      </c>
-      <c r="F368" t="s" s="13">
-        <v>569</v>
-      </c>
+      <c r="F368" s="14"/>
     </row>
     <row r="369" ht="20.05" customHeight="1">
       <c r="A369" t="s" s="9">
-        <v>575</v>
+        <v>412</v>
       </c>
       <c r="B369" t="s" s="9">
-        <v>576</v>
+        <v>458</v>
       </c>
       <c r="C369" t="s" s="10">
-        <v>577</v>
+        <v>459</v>
       </c>
       <c r="D369" s="11">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="E369" s="12">
         <v>46193</v>
       </c>
       <c r="F369" t="s" s="13">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="370" ht="20.05" customHeight="1">
       <c r="A370" t="s" s="9">
-        <v>412</v>
+        <v>577</v>
       </c>
       <c r="B370" t="s" s="9">
-        <v>458</v>
+        <v>578</v>
       </c>
       <c r="C370" t="s" s="10">
-        <v>459</v>
+        <v>579</v>
       </c>
       <c r="D370" s="11">
         <v>46193</v>
       </c>
       <c r="E370" s="12">
-        <v>46194</v>
+        <v>46193</v>
       </c>
       <c r="F370" t="s" s="13">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="371" ht="20.05" customHeight="1">
       <c r="A371" t="s" s="9">
-        <v>578</v>
+        <v>412</v>
       </c>
       <c r="B371" t="s" s="9">
-        <v>579</v>
+        <v>458</v>
       </c>
       <c r="C371" t="s" s="10">
-        <v>580</v>
+        <v>459</v>
       </c>
       <c r="D371" s="11">
+        <v>46193</v>
+      </c>
+      <c r="E371" s="12">
         <v>46194</v>
       </c>
-      <c r="E371" s="12">
-        <v>46196</v>
-      </c>
       <c r="F371" t="s" s="13">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="372" ht="20.05" customHeight="1">
       <c r="A372" t="s" s="9">
-        <v>578</v>
+        <v>292</v>
       </c>
       <c r="B372" t="s" s="9">
-        <v>581</v>
+        <v>293</v>
       </c>
       <c r="C372" t="s" s="10">
-        <v>582</v>
+        <v>294</v>
       </c>
       <c r="D372" s="11">
-        <v>46196</v>
+        <v>46194</v>
       </c>
       <c r="E372" s="12">
-        <v>46197</v>
+        <v>46227</v>
       </c>
       <c r="F372" t="s" s="13">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="373" ht="20.05" customHeight="1">
       <c r="A373" t="s" s="9">
-        <v>578</v>
+        <v>502</v>
       </c>
       <c r="B373" t="s" s="9">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C373" t="s" s="10">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D373" s="11">
-        <v>46197</v>
+        <v>46227</v>
       </c>
       <c r="E373" s="12">
-        <v>46198</v>
+        <v>46228</v>
       </c>
       <c r="F373" t="s" s="13">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="374" ht="20.05" customHeight="1">
       <c r="A374" t="s" s="9">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B374" t="s" s="9">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C374" t="s" s="10">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D374" s="11">
-        <v>46198</v>
+        <v>46228</v>
       </c>
       <c r="E374" s="12">
-        <v>46199</v>
+        <v>46230</v>
       </c>
       <c r="F374" t="s" s="13">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="375" ht="20.05" customHeight="1">
       <c r="A375" t="s" s="9">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B375" t="s" s="9">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C375" t="s" s="10">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D375" s="11">
-        <v>46199</v>
+        <v>46230</v>
       </c>
       <c r="E375" s="12">
-        <v>46200</v>
+        <v>46231</v>
       </c>
       <c r="F375" t="s" s="13">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="376" ht="20.05" customHeight="1">
       <c r="A376" t="s" s="9">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B376" t="s" s="9">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C376" t="s" s="10">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D376" s="11">
-        <v>46200</v>
+        <v>46231</v>
       </c>
       <c r="E376" s="12">
-        <v>46203</v>
+        <v>46232</v>
       </c>
       <c r="F376" t="s" s="13">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="377" ht="20.05" customHeight="1">
       <c r="A377" t="s" s="9">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B377" t="s" s="9">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C377" t="s" s="10">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D377" s="11">
-        <v>46203</v>
+        <v>46232</v>
       </c>
       <c r="E377" s="12">
-        <v>46205</v>
+        <v>46233</v>
       </c>
       <c r="F377" t="s" s="13">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="378" ht="20.05" customHeight="1">
       <c r="A378" t="s" s="9">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B378" t="s" s="9">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C378" t="s" s="10">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D378" s="11">
-        <v>46205</v>
+        <v>46233</v>
       </c>
       <c r="E378" s="12">
-        <v>46208</v>
+        <v>46234</v>
       </c>
       <c r="F378" t="s" s="13">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="379" ht="20.05" customHeight="1">
       <c r="A379" t="s" s="9">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B379" t="s" s="9">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C379" t="s" s="10">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D379" s="11">
-        <v>46208</v>
+        <v>46234</v>
       </c>
       <c r="E379" s="12">
-        <v>46221</v>
+        <v>46236</v>
       </c>
       <c r="F379" t="s" s="13">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="380" ht="20.05" customHeight="1">
       <c r="A380" t="s" s="9">
+        <v>582</v>
+      </c>
+      <c r="B380" t="s" s="9">
+        <v>595</v>
+      </c>
+      <c r="C380" t="s" s="10">
+        <v>596</v>
+      </c>
+      <c r="D380" s="11">
+        <v>46236</v>
+      </c>
+      <c r="E380" s="12">
+        <v>46263</v>
+      </c>
+      <c r="F380" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="381" ht="20.05" customHeight="1">
+      <c r="A381" t="s" s="9">
+        <v>582</v>
+      </c>
+      <c r="B381" t="s" s="9">
+        <v>597</v>
+      </c>
+      <c r="C381" t="s" s="10">
+        <v>598</v>
+      </c>
+      <c r="D381" s="11">
+        <v>46263</v>
+      </c>
+      <c r="E381" s="12">
+        <v>46265</v>
+      </c>
+      <c r="F381" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="382" ht="20.05" customHeight="1">
+      <c r="A382" t="s" s="9">
+        <v>582</v>
+      </c>
+      <c r="B382" t="s" s="9">
+        <v>599</v>
+      </c>
+      <c r="C382" t="s" s="10">
+        <v>600</v>
+      </c>
+      <c r="D382" s="11">
+        <v>46265</v>
+      </c>
+      <c r="E382" s="12">
+        <v>46267</v>
+      </c>
+      <c r="F382" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="383" ht="20.05" customHeight="1">
+      <c r="A383" t="s" s="9">
+        <v>582</v>
+      </c>
+      <c r="B383" t="s" s="9">
+        <v>601</v>
+      </c>
+      <c r="C383" t="s" s="10">
+        <v>602</v>
+      </c>
+      <c r="D383" s="11">
+        <v>46267</v>
+      </c>
+      <c r="E383" s="12">
+        <v>46270</v>
+      </c>
+      <c r="F383" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="384" ht="20.05" customHeight="1">
+      <c r="A384" t="s" s="9">
         <v>292</v>
       </c>
-      <c r="B380" t="s" s="9">
+      <c r="B384" t="s" s="9">
         <v>293</v>
       </c>
-      <c r="C380" t="s" s="10">
+      <c r="C384" t="s" s="10">
         <v>294</v>
       </c>
-      <c r="D380" s="11">
-        <v>46221</v>
-      </c>
-      <c r="E380" s="12">
-        <v>46234</v>
-      </c>
-      <c r="F380" s="14"/>
+      <c r="D384" s="11">
+        <v>46270</v>
+      </c>
+      <c r="E384" s="12">
+        <v>46373</v>
+      </c>
+      <c r="F384" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="385" ht="20.05" customHeight="1">
+      <c r="A385" t="s" s="9">
+        <v>603</v>
+      </c>
+      <c r="B385" t="s" s="9">
+        <v>604</v>
+      </c>
+      <c r="C385" t="s" s="10">
+        <v>605</v>
+      </c>
+      <c r="D385" s="11">
+        <v>46373</v>
+      </c>
+      <c r="E385" s="12">
+        <v>46380</v>
+      </c>
+      <c r="F385" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="386" ht="20.05" customHeight="1">
+      <c r="A386" t="s" s="9">
+        <v>603</v>
+      </c>
+      <c r="B386" t="s" s="9">
+        <v>606</v>
+      </c>
+      <c r="C386" t="s" s="10">
+        <v>607</v>
+      </c>
+      <c r="D386" s="11">
+        <v>46380</v>
+      </c>
+      <c r="E386" s="12">
+        <v>46385</v>
+      </c>
+      <c r="F386" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="387" ht="20.05" customHeight="1">
+      <c r="A387" t="s" s="9">
+        <v>608</v>
+      </c>
+      <c r="B387" t="s" s="9">
+        <v>609</v>
+      </c>
+      <c r="C387" t="s" s="10">
+        <v>610</v>
+      </c>
+      <c r="D387" s="11">
+        <v>46385</v>
+      </c>
+      <c r="E387" s="12">
+        <v>46388</v>
+      </c>
+      <c r="F387" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="388" ht="20.05" customHeight="1">
+      <c r="A388" t="s" s="9">
+        <v>608</v>
+      </c>
+      <c r="B388" t="s" s="9">
+        <v>611</v>
+      </c>
+      <c r="C388" t="s" s="10">
+        <v>612</v>
+      </c>
+      <c r="D388" s="11">
+        <v>46388</v>
+      </c>
+      <c r="E388" s="12">
+        <v>46390</v>
+      </c>
+      <c r="F388" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="389" ht="20.05" customHeight="1">
+      <c r="A389" t="s" s="9">
+        <v>613</v>
+      </c>
+      <c r="B389" t="s" s="9">
+        <v>614</v>
+      </c>
+      <c r="C389" t="s" s="10">
+        <v>615</v>
+      </c>
+      <c r="D389" s="11">
+        <v>46390</v>
+      </c>
+      <c r="E389" s="12">
+        <v>46393</v>
+      </c>
+      <c r="F389" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="390" ht="20.05" customHeight="1">
+      <c r="A390" t="s" s="9">
+        <v>616</v>
+      </c>
+      <c r="B390" t="s" s="9">
+        <v>617</v>
+      </c>
+      <c r="C390" t="s" s="10">
+        <v>618</v>
+      </c>
+      <c r="D390" s="11">
+        <v>46393</v>
+      </c>
+      <c r="E390" s="12">
+        <v>46396</v>
+      </c>
+      <c r="F390" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="391" ht="20.05" customHeight="1">
+      <c r="A391" t="s" s="9">
+        <v>292</v>
+      </c>
+      <c r="B391" t="s" s="9">
+        <v>293</v>
+      </c>
+      <c r="C391" t="s" s="10">
+        <v>294</v>
+      </c>
+      <c r="D391" s="11">
+        <v>46396</v>
+      </c>
+      <c r="E391" s="12">
+        <v>46418</v>
+      </c>
+      <c r="F391" t="s" s="13">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="392" ht="20.05" customHeight="1">
+      <c r="A392" s="16"/>
+      <c r="B392" s="16"/>
+      <c r="C392" s="17"/>
+      <c r="D392" s="18"/>
+      <c r="E392" s="14"/>
+      <c r="F392" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="621">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1739,6 +1739,12 @@
   </si>
   <si>
     <t>43.2141° N, 27.9147° E</t>
+  </si>
+  <si>
+    <t>Cologne</t>
+  </si>
+  <si>
+    <t>50.9375° N, 6.9603° E</t>
   </si>
   <si>
     <t>TBD</t>
@@ -9803,68 +9809,68 @@
         <v>46179</v>
       </c>
       <c r="E368" s="12">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="F368" s="14"/>
     </row>
     <row r="369" ht="20.05" customHeight="1">
       <c r="A369" t="s" s="9">
-        <v>412</v>
+        <v>331</v>
       </c>
       <c r="B369" t="s" s="9">
-        <v>458</v>
+        <v>576</v>
       </c>
       <c r="C369" t="s" s="10">
-        <v>459</v>
+        <v>577</v>
       </c>
       <c r="D369" s="11">
+        <v>46191</v>
+      </c>
+      <c r="E369" s="12">
         <v>46192</v>
       </c>
-      <c r="E369" s="12">
-        <v>46193</v>
-      </c>
       <c r="F369" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="370" ht="20.05" customHeight="1">
       <c r="A370" t="s" s="9">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B370" t="s" s="9">
+        <v>580</v>
+      </c>
+      <c r="C370" t="s" s="10">
+        <v>581</v>
+      </c>
+      <c r="D370" s="11">
+        <v>46192</v>
+      </c>
+      <c r="E370" s="12">
+        <v>46192</v>
+      </c>
+      <c r="F370" t="s" s="13">
         <v>578</v>
-      </c>
-      <c r="C370" t="s" s="10">
-        <v>579</v>
-      </c>
-      <c r="D370" s="11">
-        <v>46193</v>
-      </c>
-      <c r="E370" s="12">
-        <v>46193</v>
-      </c>
-      <c r="F370" t="s" s="13">
-        <v>576</v>
       </c>
     </row>
     <row r="371" ht="20.05" customHeight="1">
       <c r="A371" t="s" s="9">
-        <v>412</v>
+        <v>331</v>
       </c>
       <c r="B371" t="s" s="9">
-        <v>458</v>
+        <v>576</v>
       </c>
       <c r="C371" t="s" s="10">
-        <v>459</v>
+        <v>577</v>
       </c>
       <c r="D371" s="11">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="E371" s="12">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="F371" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="372" ht="20.05" customHeight="1">
@@ -9878,13 +9884,13 @@
         <v>294</v>
       </c>
       <c r="D372" s="11">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="E372" s="12">
         <v>46227</v>
       </c>
       <c r="F372" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="373" ht="20.05" customHeight="1">
@@ -9892,10 +9898,10 @@
         <v>502</v>
       </c>
       <c r="B373" t="s" s="9">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C373" t="s" s="10">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D373" s="11">
         <v>46227</v>
@@ -9904,18 +9910,18 @@
         <v>46228</v>
       </c>
       <c r="F373" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="374" ht="20.05" customHeight="1">
       <c r="A374" t="s" s="9">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B374" t="s" s="9">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C374" t="s" s="10">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D374" s="11">
         <v>46228</v>
@@ -9924,18 +9930,18 @@
         <v>46230</v>
       </c>
       <c r="F374" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="375" ht="20.05" customHeight="1">
       <c r="A375" t="s" s="9">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B375" t="s" s="9">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C375" t="s" s="10">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D375" s="11">
         <v>46230</v>
@@ -9944,18 +9950,18 @@
         <v>46231</v>
       </c>
       <c r="F375" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="376" ht="20.05" customHeight="1">
       <c r="A376" t="s" s="9">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B376" t="s" s="9">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C376" t="s" s="10">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D376" s="11">
         <v>46231</v>
@@ -9964,18 +9970,18 @@
         <v>46232</v>
       </c>
       <c r="F376" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="377" ht="20.05" customHeight="1">
       <c r="A377" t="s" s="9">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B377" t="s" s="9">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C377" t="s" s="10">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D377" s="11">
         <v>46232</v>
@@ -9984,18 +9990,18 @@
         <v>46233</v>
       </c>
       <c r="F377" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="378" ht="20.05" customHeight="1">
       <c r="A378" t="s" s="9">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B378" t="s" s="9">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C378" t="s" s="10">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D378" s="11">
         <v>46233</v>
@@ -10004,18 +10010,18 @@
         <v>46234</v>
       </c>
       <c r="F378" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="379" ht="20.05" customHeight="1">
       <c r="A379" t="s" s="9">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B379" t="s" s="9">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C379" t="s" s="10">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D379" s="11">
         <v>46234</v>
@@ -10024,18 +10030,18 @@
         <v>46236</v>
       </c>
       <c r="F379" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="380" ht="20.05" customHeight="1">
       <c r="A380" t="s" s="9">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B380" t="s" s="9">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C380" t="s" s="10">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D380" s="11">
         <v>46236</v>
@@ -10044,18 +10050,18 @@
         <v>46263</v>
       </c>
       <c r="F380" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="381" ht="20.05" customHeight="1">
       <c r="A381" t="s" s="9">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B381" t="s" s="9">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C381" t="s" s="10">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D381" s="11">
         <v>46263</v>
@@ -10064,18 +10070,18 @@
         <v>46265</v>
       </c>
       <c r="F381" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="382" ht="20.05" customHeight="1">
       <c r="A382" t="s" s="9">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B382" t="s" s="9">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C382" t="s" s="10">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D382" s="11">
         <v>46265</v>
@@ -10084,18 +10090,18 @@
         <v>46267</v>
       </c>
       <c r="F382" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="383" ht="20.05" customHeight="1">
       <c r="A383" t="s" s="9">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B383" t="s" s="9">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C383" t="s" s="10">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D383" s="11">
         <v>46267</v>
@@ -10104,7 +10110,7 @@
         <v>46270</v>
       </c>
       <c r="F383" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="384" ht="20.05" customHeight="1">
@@ -10124,18 +10130,18 @@
         <v>46373</v>
       </c>
       <c r="F384" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="385" ht="20.05" customHeight="1">
       <c r="A385" t="s" s="9">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B385" t="s" s="9">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C385" t="s" s="10">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D385" s="11">
         <v>46373</v>
@@ -10144,18 +10150,18 @@
         <v>46380</v>
       </c>
       <c r="F385" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="386" ht="20.05" customHeight="1">
       <c r="A386" t="s" s="9">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B386" t="s" s="9">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C386" t="s" s="10">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D386" s="11">
         <v>46380</v>
@@ -10164,18 +10170,18 @@
         <v>46385</v>
       </c>
       <c r="F386" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="387" ht="20.05" customHeight="1">
       <c r="A387" t="s" s="9">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B387" t="s" s="9">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C387" t="s" s="10">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D387" s="11">
         <v>46385</v>
@@ -10184,18 +10190,18 @@
         <v>46388</v>
       </c>
       <c r="F387" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="388" ht="20.05" customHeight="1">
       <c r="A388" t="s" s="9">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B388" t="s" s="9">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C388" t="s" s="10">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D388" s="11">
         <v>46388</v>
@@ -10204,18 +10210,18 @@
         <v>46390</v>
       </c>
       <c r="F388" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="389" ht="20.05" customHeight="1">
       <c r="A389" t="s" s="9">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B389" t="s" s="9">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C389" t="s" s="10">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D389" s="11">
         <v>46390</v>
@@ -10224,18 +10230,18 @@
         <v>46393</v>
       </c>
       <c r="F389" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="390" ht="20.05" customHeight="1">
       <c r="A390" t="s" s="9">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B390" t="s" s="9">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C390" t="s" s="10">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D390" s="11">
         <v>46393</v>
@@ -10244,7 +10250,7 @@
         <v>46396</v>
       </c>
       <c r="F390" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="391" ht="20.05" customHeight="1">
@@ -10264,7 +10270,7 @@
         <v>46418</v>
       </c>
       <c r="F391" t="s" s="13">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="392" ht="20.05" customHeight="1">

--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="623">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1739,6 +1739,12 @@
   </si>
   <si>
     <t>43.2141° N, 27.9147° E</t>
+  </si>
+  <si>
+    <t>Frankfurt am Main</t>
+  </si>
+  <si>
+    <t>50.1109° N, 8.6821° E</t>
   </si>
   <si>
     <t>Cologne</t>
@@ -3145,7 +3151,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F392"/>
+  <dimension ref="A2:F393"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -9797,145 +9803,143 @@
     </row>
     <row r="368" ht="20.05" customHeight="1">
       <c r="A368" t="s" s="9">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="B368" t="s" s="9">
-        <v>293</v>
+        <v>576</v>
       </c>
       <c r="C368" t="s" s="10">
-        <v>294</v>
+        <v>577</v>
       </c>
       <c r="D368" s="11">
         <v>46179</v>
       </c>
       <c r="E368" s="12">
-        <v>46191</v>
+        <v>46179</v>
       </c>
       <c r="F368" s="14"/>
     </row>
     <row r="369" ht="20.05" customHeight="1">
       <c r="A369" t="s" s="9">
-        <v>331</v>
+        <v>292</v>
       </c>
       <c r="B369" t="s" s="9">
-        <v>576</v>
+        <v>293</v>
       </c>
       <c r="C369" t="s" s="10">
-        <v>577</v>
+        <v>294</v>
       </c>
       <c r="D369" s="11">
+        <v>46179</v>
+      </c>
+      <c r="E369" s="12">
         <v>46191</v>
       </c>
-      <c r="E369" s="12">
-        <v>46192</v>
-      </c>
-      <c r="F369" t="s" s="13">
-        <v>578</v>
-      </c>
+      <c r="F369" s="14"/>
     </row>
     <row r="370" ht="20.05" customHeight="1">
       <c r="A370" t="s" s="9">
+        <v>331</v>
+      </c>
+      <c r="B370" t="s" s="9">
+        <v>578</v>
+      </c>
+      <c r="C370" t="s" s="10">
         <v>579</v>
       </c>
-      <c r="B370" t="s" s="9">
-        <v>580</v>
-      </c>
-      <c r="C370" t="s" s="10">
-        <v>581</v>
-      </c>
       <c r="D370" s="11">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="E370" s="12">
         <v>46192</v>
       </c>
       <c r="F370" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="371" ht="20.05" customHeight="1">
       <c r="A371" t="s" s="9">
-        <v>331</v>
+        <v>581</v>
       </c>
       <c r="B371" t="s" s="9">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C371" t="s" s="10">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="D371" s="11">
         <v>46192</v>
       </c>
       <c r="E371" s="12">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="F371" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="372" ht="20.05" customHeight="1">
       <c r="A372" t="s" s="9">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="B372" t="s" s="9">
-        <v>293</v>
+        <v>578</v>
       </c>
       <c r="C372" t="s" s="10">
-        <v>294</v>
+        <v>579</v>
       </c>
       <c r="D372" s="11">
+        <v>46192</v>
+      </c>
+      <c r="E372" s="12">
         <v>46195</v>
       </c>
-      <c r="E372" s="12">
-        <v>46227</v>
-      </c>
       <c r="F372" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="373" ht="20.05" customHeight="1">
       <c r="A373" t="s" s="9">
-        <v>502</v>
+        <v>292</v>
       </c>
       <c r="B373" t="s" s="9">
-        <v>582</v>
+        <v>293</v>
       </c>
       <c r="C373" t="s" s="10">
-        <v>583</v>
+        <v>294</v>
       </c>
       <c r="D373" s="11">
+        <v>46195</v>
+      </c>
+      <c r="E373" s="12">
         <v>46227</v>
       </c>
-      <c r="E373" s="12">
-        <v>46228</v>
-      </c>
       <c r="F373" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="374" ht="20.05" customHeight="1">
       <c r="A374" t="s" s="9">
+        <v>502</v>
+      </c>
+      <c r="B374" t="s" s="9">
         <v>584</v>
       </c>
-      <c r="B374" t="s" s="9">
+      <c r="C374" t="s" s="10">
         <v>585</v>
       </c>
-      <c r="C374" t="s" s="10">
-        <v>586</v>
-      </c>
       <c r="D374" s="11">
+        <v>46227</v>
+      </c>
+      <c r="E374" s="12">
         <v>46228</v>
       </c>
-      <c r="E374" s="12">
-        <v>46230</v>
-      </c>
       <c r="F374" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="375" ht="20.05" customHeight="1">
       <c r="A375" t="s" s="9">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B375" t="s" s="9">
         <v>587</v>
@@ -9944,18 +9948,18 @@
         <v>588</v>
       </c>
       <c r="D375" s="11">
+        <v>46228</v>
+      </c>
+      <c r="E375" s="12">
         <v>46230</v>
       </c>
-      <c r="E375" s="12">
-        <v>46231</v>
-      </c>
       <c r="F375" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="376" ht="20.05" customHeight="1">
       <c r="A376" t="s" s="9">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B376" t="s" s="9">
         <v>589</v>
@@ -9964,18 +9968,18 @@
         <v>590</v>
       </c>
       <c r="D376" s="11">
+        <v>46230</v>
+      </c>
+      <c r="E376" s="12">
         <v>46231</v>
       </c>
-      <c r="E376" s="12">
-        <v>46232</v>
-      </c>
       <c r="F376" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="377" ht="20.05" customHeight="1">
       <c r="A377" t="s" s="9">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B377" t="s" s="9">
         <v>591</v>
@@ -9984,18 +9988,18 @@
         <v>592</v>
       </c>
       <c r="D377" s="11">
+        <v>46231</v>
+      </c>
+      <c r="E377" s="12">
         <v>46232</v>
       </c>
-      <c r="E377" s="12">
-        <v>46233</v>
-      </c>
       <c r="F377" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="378" ht="20.05" customHeight="1">
       <c r="A378" t="s" s="9">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B378" t="s" s="9">
         <v>593</v>
@@ -10004,18 +10008,18 @@
         <v>594</v>
       </c>
       <c r="D378" s="11">
+        <v>46232</v>
+      </c>
+      <c r="E378" s="12">
         <v>46233</v>
       </c>
-      <c r="E378" s="12">
-        <v>46234</v>
-      </c>
       <c r="F378" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="379" ht="20.05" customHeight="1">
       <c r="A379" t="s" s="9">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B379" t="s" s="9">
         <v>595</v>
@@ -10024,18 +10028,18 @@
         <v>596</v>
       </c>
       <c r="D379" s="11">
+        <v>46233</v>
+      </c>
+      <c r="E379" s="12">
         <v>46234</v>
       </c>
-      <c r="E379" s="12">
-        <v>46236</v>
-      </c>
       <c r="F379" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="380" ht="20.05" customHeight="1">
       <c r="A380" t="s" s="9">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B380" t="s" s="9">
         <v>597</v>
@@ -10044,18 +10048,18 @@
         <v>598</v>
       </c>
       <c r="D380" s="11">
+        <v>46234</v>
+      </c>
+      <c r="E380" s="12">
         <v>46236</v>
       </c>
-      <c r="E380" s="12">
-        <v>46263</v>
-      </c>
       <c r="F380" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="381" ht="20.05" customHeight="1">
       <c r="A381" t="s" s="9">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B381" t="s" s="9">
         <v>599</v>
@@ -10064,18 +10068,18 @@
         <v>600</v>
       </c>
       <c r="D381" s="11">
+        <v>46236</v>
+      </c>
+      <c r="E381" s="12">
         <v>46263</v>
       </c>
-      <c r="E381" s="12">
-        <v>46265</v>
-      </c>
       <c r="F381" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="382" ht="20.05" customHeight="1">
       <c r="A382" t="s" s="9">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B382" t="s" s="9">
         <v>601</v>
@@ -10084,18 +10088,18 @@
         <v>602</v>
       </c>
       <c r="D382" s="11">
+        <v>46263</v>
+      </c>
+      <c r="E382" s="12">
         <v>46265</v>
       </c>
-      <c r="E382" s="12">
-        <v>46267</v>
-      </c>
       <c r="F382" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="383" ht="20.05" customHeight="1">
       <c r="A383" t="s" s="9">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B383" t="s" s="9">
         <v>603</v>
@@ -10104,58 +10108,58 @@
         <v>604</v>
       </c>
       <c r="D383" s="11">
+        <v>46265</v>
+      </c>
+      <c r="E383" s="12">
         <v>46267</v>
       </c>
-      <c r="E383" s="12">
-        <v>46270</v>
-      </c>
       <c r="F383" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="384" ht="20.05" customHeight="1">
       <c r="A384" t="s" s="9">
-        <v>292</v>
+        <v>586</v>
       </c>
       <c r="B384" t="s" s="9">
-        <v>293</v>
+        <v>605</v>
       </c>
       <c r="C384" t="s" s="10">
-        <v>294</v>
+        <v>606</v>
       </c>
       <c r="D384" s="11">
+        <v>46267</v>
+      </c>
+      <c r="E384" s="12">
         <v>46270</v>
       </c>
-      <c r="E384" s="12">
-        <v>46373</v>
-      </c>
       <c r="F384" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="385" ht="20.05" customHeight="1">
       <c r="A385" t="s" s="9">
-        <v>605</v>
+        <v>292</v>
       </c>
       <c r="B385" t="s" s="9">
-        <v>606</v>
+        <v>293</v>
       </c>
       <c r="C385" t="s" s="10">
-        <v>607</v>
+        <v>294</v>
       </c>
       <c r="D385" s="11">
+        <v>46270</v>
+      </c>
+      <c r="E385" s="12">
         <v>46373</v>
       </c>
-      <c r="E385" s="12">
-        <v>46380</v>
-      </c>
       <c r="F385" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="386" ht="20.05" customHeight="1">
       <c r="A386" t="s" s="9">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B386" t="s" s="9">
         <v>608</v>
@@ -10164,38 +10168,38 @@
         <v>609</v>
       </c>
       <c r="D386" s="11">
+        <v>46373</v>
+      </c>
+      <c r="E386" s="12">
         <v>46380</v>
       </c>
-      <c r="E386" s="12">
-        <v>46385</v>
-      </c>
       <c r="F386" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="387" ht="20.05" customHeight="1">
       <c r="A387" t="s" s="9">
+        <v>607</v>
+      </c>
+      <c r="B387" t="s" s="9">
         <v>610</v>
       </c>
-      <c r="B387" t="s" s="9">
+      <c r="C387" t="s" s="10">
         <v>611</v>
       </c>
-      <c r="C387" t="s" s="10">
-        <v>612</v>
-      </c>
       <c r="D387" s="11">
+        <v>46380</v>
+      </c>
+      <c r="E387" s="12">
         <v>46385</v>
       </c>
-      <c r="E387" s="12">
-        <v>46388</v>
-      </c>
       <c r="F387" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="388" ht="20.05" customHeight="1">
       <c r="A388" t="s" s="9">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B388" t="s" s="9">
         <v>613</v>
@@ -10204,82 +10208,102 @@
         <v>614</v>
       </c>
       <c r="D388" s="11">
+        <v>46385</v>
+      </c>
+      <c r="E388" s="12">
         <v>46388</v>
       </c>
-      <c r="E388" s="12">
-        <v>46390</v>
-      </c>
       <c r="F388" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="389" ht="20.05" customHeight="1">
       <c r="A389" t="s" s="9">
+        <v>612</v>
+      </c>
+      <c r="B389" t="s" s="9">
         <v>615</v>
       </c>
-      <c r="B389" t="s" s="9">
+      <c r="C389" t="s" s="10">
         <v>616</v>
       </c>
-      <c r="C389" t="s" s="10">
-        <v>617</v>
-      </c>
       <c r="D389" s="11">
+        <v>46388</v>
+      </c>
+      <c r="E389" s="12">
         <v>46390</v>
       </c>
-      <c r="E389" s="12">
-        <v>46393</v>
-      </c>
       <c r="F389" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="390" ht="20.05" customHeight="1">
       <c r="A390" t="s" s="9">
+        <v>617</v>
+      </c>
+      <c r="B390" t="s" s="9">
         <v>618</v>
       </c>
-      <c r="B390" t="s" s="9">
+      <c r="C390" t="s" s="10">
         <v>619</v>
       </c>
-      <c r="C390" t="s" s="10">
-        <v>620</v>
-      </c>
       <c r="D390" s="11">
+        <v>46390</v>
+      </c>
+      <c r="E390" s="12">
         <v>46393</v>
       </c>
-      <c r="E390" s="12">
-        <v>46396</v>
-      </c>
       <c r="F390" t="s" s="13">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="391" ht="20.05" customHeight="1">
       <c r="A391" t="s" s="9">
+        <v>620</v>
+      </c>
+      <c r="B391" t="s" s="9">
+        <v>621</v>
+      </c>
+      <c r="C391" t="s" s="10">
+        <v>622</v>
+      </c>
+      <c r="D391" s="11">
+        <v>46393</v>
+      </c>
+      <c r="E391" s="12">
+        <v>46396</v>
+      </c>
+      <c r="F391" t="s" s="13">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="392" ht="20.05" customHeight="1">
+      <c r="A392" t="s" s="9">
         <v>292</v>
       </c>
-      <c r="B391" t="s" s="9">
+      <c r="B392" t="s" s="9">
         <v>293</v>
       </c>
-      <c r="C391" t="s" s="10">
+      <c r="C392" t="s" s="10">
         <v>294</v>
       </c>
-      <c r="D391" s="11">
+      <c r="D392" s="11">
         <v>46396</v>
       </c>
-      <c r="E391" s="12">
+      <c r="E392" s="12">
         <v>46418</v>
       </c>
-      <c r="F391" t="s" s="13">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="392" ht="20.05" customHeight="1">
-      <c r="A392" s="16"/>
-      <c r="B392" s="16"/>
-      <c r="C392" s="17"/>
-      <c r="D392" s="18"/>
-      <c r="E392" s="14"/>
-      <c r="F392" s="14"/>
+      <c r="F392" t="s" s="13">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="393" ht="20.05" customHeight="1">
+      <c r="A393" s="16"/>
+      <c r="B393" s="16"/>
+      <c r="C393" s="17"/>
+      <c r="D393" s="18"/>
+      <c r="E393" s="14"/>
+      <c r="F393" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="627">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1747,28 +1747,40 @@
     <t>50.1109° N, 8.6821° E</t>
   </si>
   <si>
+    <t>Düsseldorf</t>
+  </si>
+  <si>
+    <t>51.2230° N, 6.7825° E</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Luxembourg City</t>
+  </si>
+  <si>
+    <t>49.8153° N, 6.1296° E</t>
+  </si>
+  <si>
     <t>Cologne</t>
   </si>
   <si>
     <t>50.9375° N, 6.9603° E</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Luxembourg</t>
-  </si>
-  <si>
-    <t>Luxembourg City</t>
-  </si>
-  <si>
-    <t>49.8153° N, 6.1296° E</t>
-  </si>
-  <si>
-    <t>Málaga</t>
-  </si>
-  <si>
-    <t>36.7178° N, 4.4256° W</t>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>43.7102° N, 7.2620° E</t>
+  </si>
+  <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>43.7384° N, 7.4246° E</t>
   </si>
   <si>
     <t>Morocco</t>
@@ -3151,7 +3163,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F393"/>
+  <dimension ref="A2:F399"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -9833,7 +9845,7 @@
         <v>46179</v>
       </c>
       <c r="E369" s="12">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="F369" s="14"/>
     </row>
@@ -9848,7 +9860,7 @@
         <v>579</v>
       </c>
       <c r="D370" s="11">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="E370" s="12">
         <v>46192</v>
@@ -9891,7 +9903,7 @@
         <v>46192</v>
       </c>
       <c r="E372" s="12">
-        <v>46195</v>
+        <v>46193</v>
       </c>
       <c r="F372" t="s" s="13">
         <v>580</v>
@@ -9899,19 +9911,19 @@
     </row>
     <row r="373" ht="20.05" customHeight="1">
       <c r="A373" t="s" s="9">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="B373" t="s" s="9">
-        <v>293</v>
+        <v>584</v>
       </c>
       <c r="C373" t="s" s="10">
-        <v>294</v>
+        <v>585</v>
       </c>
       <c r="D373" s="11">
-        <v>46195</v>
+        <v>46193</v>
       </c>
       <c r="E373" s="12">
-        <v>46227</v>
+        <v>46193</v>
       </c>
       <c r="F373" t="s" s="13">
         <v>580</v>
@@ -9919,19 +9931,19 @@
     </row>
     <row r="374" ht="20.05" customHeight="1">
       <c r="A374" t="s" s="9">
-        <v>502</v>
+        <v>331</v>
       </c>
       <c r="B374" t="s" s="9">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C374" t="s" s="10">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="D374" s="11">
-        <v>46227</v>
+        <v>46193</v>
       </c>
       <c r="E374" s="12">
-        <v>46228</v>
+        <v>46194</v>
       </c>
       <c r="F374" t="s" s="13">
         <v>580</v>
@@ -9939,19 +9951,19 @@
     </row>
     <row r="375" ht="20.05" customHeight="1">
       <c r="A375" t="s" s="9">
-        <v>586</v>
+        <v>331</v>
       </c>
       <c r="B375" t="s" s="9">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C375" t="s" s="10">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D375" s="11">
-        <v>46228</v>
+        <v>46194</v>
       </c>
       <c r="E375" s="12">
-        <v>46230</v>
+        <v>46194</v>
       </c>
       <c r="F375" t="s" s="13">
         <v>580</v>
@@ -9959,19 +9971,19 @@
     </row>
     <row r="376" ht="20.05" customHeight="1">
       <c r="A376" t="s" s="9">
-        <v>586</v>
+        <v>331</v>
       </c>
       <c r="B376" t="s" s="9">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="C376" t="s" s="10">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="D376" s="11">
-        <v>46230</v>
+        <v>46194</v>
       </c>
       <c r="E376" s="12">
-        <v>46231</v>
+        <v>46195</v>
       </c>
       <c r="F376" t="s" s="13">
         <v>580</v>
@@ -9979,19 +9991,19 @@
     </row>
     <row r="377" ht="20.05" customHeight="1">
       <c r="A377" t="s" s="9">
-        <v>586</v>
+        <v>292</v>
       </c>
       <c r="B377" t="s" s="9">
-        <v>591</v>
+        <v>293</v>
       </c>
       <c r="C377" t="s" s="10">
-        <v>592</v>
+        <v>294</v>
       </c>
       <c r="D377" s="11">
-        <v>46231</v>
+        <v>46195</v>
       </c>
       <c r="E377" s="12">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="F377" t="s" s="13">
         <v>580</v>
@@ -9999,19 +10011,19 @@
     </row>
     <row r="378" ht="20.05" customHeight="1">
       <c r="A378" t="s" s="9">
+        <v>460</v>
+      </c>
+      <c r="B378" t="s" s="9">
         <v>586</v>
       </c>
-      <c r="B378" t="s" s="9">
-        <v>593</v>
-      </c>
       <c r="C378" t="s" s="10">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="D378" s="11">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="E378" s="12">
-        <v>46233</v>
+        <v>46228</v>
       </c>
       <c r="F378" t="s" s="13">
         <v>580</v>
@@ -10019,19 +10031,19 @@
     </row>
     <row r="379" ht="20.05" customHeight="1">
       <c r="A379" t="s" s="9">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B379" t="s" s="9">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="C379" t="s" s="10">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="D379" s="11">
-        <v>46233</v>
+        <v>46228</v>
       </c>
       <c r="E379" s="12">
-        <v>46234</v>
+        <v>46228</v>
       </c>
       <c r="F379" t="s" s="13">
         <v>580</v>
@@ -10039,19 +10051,19 @@
     </row>
     <row r="380" ht="20.05" customHeight="1">
       <c r="A380" t="s" s="9">
+        <v>460</v>
+      </c>
+      <c r="B380" t="s" s="9">
         <v>586</v>
       </c>
-      <c r="B380" t="s" s="9">
-        <v>597</v>
-      </c>
       <c r="C380" t="s" s="10">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D380" s="11">
-        <v>46234</v>
+        <v>46228</v>
       </c>
       <c r="E380" s="12">
-        <v>46236</v>
+        <v>46229</v>
       </c>
       <c r="F380" t="s" s="13">
         <v>580</v>
@@ -10059,19 +10071,19 @@
     </row>
     <row r="381" ht="20.05" customHeight="1">
       <c r="A381" t="s" s="9">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B381" t="s" s="9">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="C381" t="s" s="10">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="D381" s="11">
-        <v>46236</v>
+        <v>46229</v>
       </c>
       <c r="E381" s="12">
-        <v>46263</v>
+        <v>46230</v>
       </c>
       <c r="F381" t="s" s="13">
         <v>580</v>
@@ -10079,19 +10091,19 @@
     </row>
     <row r="382" ht="20.05" customHeight="1">
       <c r="A382" t="s" s="9">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B382" t="s" s="9">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="C382" t="s" s="10">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="D382" s="11">
-        <v>46263</v>
+        <v>46230</v>
       </c>
       <c r="E382" s="12">
-        <v>46265</v>
+        <v>46231</v>
       </c>
       <c r="F382" t="s" s="13">
         <v>580</v>
@@ -10099,19 +10111,19 @@
     </row>
     <row r="383" ht="20.05" customHeight="1">
       <c r="A383" t="s" s="9">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B383" t="s" s="9">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C383" t="s" s="10">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D383" s="11">
-        <v>46265</v>
+        <v>46231</v>
       </c>
       <c r="E383" s="12">
-        <v>46267</v>
+        <v>46232</v>
       </c>
       <c r="F383" t="s" s="13">
         <v>580</v>
@@ -10119,19 +10131,19 @@
     </row>
     <row r="384" ht="20.05" customHeight="1">
       <c r="A384" t="s" s="9">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B384" t="s" s="9">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="C384" t="s" s="10">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="D384" s="11">
-        <v>46267</v>
+        <v>46232</v>
       </c>
       <c r="E384" s="12">
-        <v>46270</v>
+        <v>46233</v>
       </c>
       <c r="F384" t="s" s="13">
         <v>580</v>
@@ -10139,19 +10151,19 @@
     </row>
     <row r="385" ht="20.05" customHeight="1">
       <c r="A385" t="s" s="9">
-        <v>292</v>
+        <v>590</v>
       </c>
       <c r="B385" t="s" s="9">
-        <v>293</v>
+        <v>599</v>
       </c>
       <c r="C385" t="s" s="10">
-        <v>294</v>
+        <v>600</v>
       </c>
       <c r="D385" s="11">
-        <v>46270</v>
+        <v>46233</v>
       </c>
       <c r="E385" s="12">
-        <v>46373</v>
+        <v>46234</v>
       </c>
       <c r="F385" t="s" s="13">
         <v>580</v>
@@ -10159,19 +10171,19 @@
     </row>
     <row r="386" ht="20.05" customHeight="1">
       <c r="A386" t="s" s="9">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="B386" t="s" s="9">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="C386" t="s" s="10">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="D386" s="11">
-        <v>46373</v>
+        <v>46234</v>
       </c>
       <c r="E386" s="12">
-        <v>46380</v>
+        <v>46236</v>
       </c>
       <c r="F386" t="s" s="13">
         <v>580</v>
@@ -10179,19 +10191,19 @@
     </row>
     <row r="387" ht="20.05" customHeight="1">
       <c r="A387" t="s" s="9">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="B387" t="s" s="9">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="C387" t="s" s="10">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="D387" s="11">
-        <v>46380</v>
+        <v>46236</v>
       </c>
       <c r="E387" s="12">
-        <v>46385</v>
+        <v>46263</v>
       </c>
       <c r="F387" t="s" s="13">
         <v>580</v>
@@ -10199,19 +10211,19 @@
     </row>
     <row r="388" ht="20.05" customHeight="1">
       <c r="A388" t="s" s="9">
-        <v>612</v>
+        <v>590</v>
       </c>
       <c r="B388" t="s" s="9">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="C388" t="s" s="10">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="D388" s="11">
-        <v>46385</v>
+        <v>46263</v>
       </c>
       <c r="E388" s="12">
-        <v>46388</v>
+        <v>46265</v>
       </c>
       <c r="F388" t="s" s="13">
         <v>580</v>
@@ -10219,19 +10231,19 @@
     </row>
     <row r="389" ht="20.05" customHeight="1">
       <c r="A389" t="s" s="9">
-        <v>612</v>
+        <v>590</v>
       </c>
       <c r="B389" t="s" s="9">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C389" t="s" s="10">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="D389" s="11">
-        <v>46388</v>
+        <v>46265</v>
       </c>
       <c r="E389" s="12">
-        <v>46390</v>
+        <v>46267</v>
       </c>
       <c r="F389" t="s" s="13">
         <v>580</v>
@@ -10239,19 +10251,19 @@
     </row>
     <row r="390" ht="20.05" customHeight="1">
       <c r="A390" t="s" s="9">
-        <v>617</v>
+        <v>590</v>
       </c>
       <c r="B390" t="s" s="9">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="C390" t="s" s="10">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="D390" s="11">
-        <v>46390</v>
+        <v>46267</v>
       </c>
       <c r="E390" s="12">
-        <v>46393</v>
+        <v>46270</v>
       </c>
       <c r="F390" t="s" s="13">
         <v>580</v>
@@ -10259,19 +10271,19 @@
     </row>
     <row r="391" ht="20.05" customHeight="1">
       <c r="A391" t="s" s="9">
-        <v>620</v>
+        <v>292</v>
       </c>
       <c r="B391" t="s" s="9">
-        <v>621</v>
+        <v>293</v>
       </c>
       <c r="C391" t="s" s="10">
-        <v>622</v>
+        <v>294</v>
       </c>
       <c r="D391" s="11">
-        <v>46393</v>
+        <v>46270</v>
       </c>
       <c r="E391" s="12">
-        <v>46396</v>
+        <v>46373</v>
       </c>
       <c r="F391" t="s" s="13">
         <v>580</v>
@@ -10279,31 +10291,151 @@
     </row>
     <row r="392" ht="20.05" customHeight="1">
       <c r="A392" t="s" s="9">
-        <v>292</v>
+        <v>611</v>
       </c>
       <c r="B392" t="s" s="9">
-        <v>293</v>
+        <v>612</v>
       </c>
       <c r="C392" t="s" s="10">
-        <v>294</v>
+        <v>613</v>
       </c>
       <c r="D392" s="11">
-        <v>46396</v>
+        <v>46373</v>
       </c>
       <c r="E392" s="12">
-        <v>46418</v>
+        <v>46380</v>
       </c>
       <c r="F392" t="s" s="13">
         <v>580</v>
       </c>
     </row>
     <row r="393" ht="20.05" customHeight="1">
-      <c r="A393" s="16"/>
-      <c r="B393" s="16"/>
-      <c r="C393" s="17"/>
-      <c r="D393" s="18"/>
-      <c r="E393" s="14"/>
-      <c r="F393" s="14"/>
+      <c r="A393" t="s" s="9">
+        <v>611</v>
+      </c>
+      <c r="B393" t="s" s="9">
+        <v>614</v>
+      </c>
+      <c r="C393" t="s" s="10">
+        <v>615</v>
+      </c>
+      <c r="D393" s="11">
+        <v>46380</v>
+      </c>
+      <c r="E393" s="12">
+        <v>46385</v>
+      </c>
+      <c r="F393" t="s" s="13">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="394" ht="20.05" customHeight="1">
+      <c r="A394" t="s" s="9">
+        <v>616</v>
+      </c>
+      <c r="B394" t="s" s="9">
+        <v>617</v>
+      </c>
+      <c r="C394" t="s" s="10">
+        <v>618</v>
+      </c>
+      <c r="D394" s="11">
+        <v>46385</v>
+      </c>
+      <c r="E394" s="12">
+        <v>46388</v>
+      </c>
+      <c r="F394" t="s" s="13">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="395" ht="20.05" customHeight="1">
+      <c r="A395" t="s" s="9">
+        <v>616</v>
+      </c>
+      <c r="B395" t="s" s="9">
+        <v>619</v>
+      </c>
+      <c r="C395" t="s" s="10">
+        <v>620</v>
+      </c>
+      <c r="D395" s="11">
+        <v>46388</v>
+      </c>
+      <c r="E395" s="12">
+        <v>46390</v>
+      </c>
+      <c r="F395" t="s" s="13">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="396" ht="20.05" customHeight="1">
+      <c r="A396" t="s" s="9">
+        <v>621</v>
+      </c>
+      <c r="B396" t="s" s="9">
+        <v>622</v>
+      </c>
+      <c r="C396" t="s" s="10">
+        <v>623</v>
+      </c>
+      <c r="D396" s="11">
+        <v>46390</v>
+      </c>
+      <c r="E396" s="12">
+        <v>46393</v>
+      </c>
+      <c r="F396" t="s" s="13">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="397" ht="20.05" customHeight="1">
+      <c r="A397" t="s" s="9">
+        <v>624</v>
+      </c>
+      <c r="B397" t="s" s="9">
+        <v>625</v>
+      </c>
+      <c r="C397" t="s" s="10">
+        <v>626</v>
+      </c>
+      <c r="D397" s="11">
+        <v>46393</v>
+      </c>
+      <c r="E397" s="12">
+        <v>46396</v>
+      </c>
+      <c r="F397" t="s" s="13">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="398" ht="20.05" customHeight="1">
+      <c r="A398" t="s" s="9">
+        <v>292</v>
+      </c>
+      <c r="B398" t="s" s="9">
+        <v>293</v>
+      </c>
+      <c r="C398" t="s" s="10">
+        <v>294</v>
+      </c>
+      <c r="D398" s="11">
+        <v>46396</v>
+      </c>
+      <c r="E398" s="12">
+        <v>46418</v>
+      </c>
+      <c r="F398" t="s" s="13">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="399" ht="20.05" customHeight="1">
+      <c r="A399" s="16"/>
+      <c r="B399" s="16"/>
+      <c r="C399" s="17"/>
+      <c r="D399" s="18"/>
+      <c r="E399" s="14"/>
+      <c r="F399" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="611">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1747,6 +1747,21 @@
     <t>50.1109° N, 8.6821° E</t>
   </si>
   <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Luxembourg City</t>
+  </si>
+  <si>
+    <t>49.8153° N, 6.1296° E</t>
+  </si>
+  <si>
+    <t>Cologne</t>
+  </si>
+  <si>
+    <t>50.9375° N, 6.9603° E</t>
+  </si>
+  <si>
     <t>Düsseldorf</t>
   </si>
   <si>
@@ -1756,21 +1771,6 @@
     <t>TBD</t>
   </si>
   <si>
-    <t>Luxembourg</t>
-  </si>
-  <si>
-    <t>Luxembourg City</t>
-  </si>
-  <si>
-    <t>49.8153° N, 6.1296° E</t>
-  </si>
-  <si>
-    <t>Cologne</t>
-  </si>
-  <si>
-    <t>50.9375° N, 6.9603° E</t>
-  </si>
-  <si>
     <t>Nice</t>
   </si>
   <si>
@@ -1844,54 +1844,6 @@
   </si>
   <si>
     <t>31.6225° N, 7.9898° W</t>
-  </si>
-  <si>
-    <t>Vietnam</t>
-  </si>
-  <si>
-    <t>Hanoi</t>
-  </si>
-  <si>
-    <t>21.0278° N, 105.8342° E</t>
-  </si>
-  <si>
-    <t>Ho Chi Minh City</t>
-  </si>
-  <si>
-    <t>10.8231° N, 106.6297° E</t>
-  </si>
-  <si>
-    <t>Cambodia</t>
-  </si>
-  <si>
-    <t>Phnom Penh</t>
-  </si>
-  <si>
-    <t>11.5564° N, 104.9282° E</t>
-  </si>
-  <si>
-    <t>Krong Siem Reap</t>
-  </si>
-  <si>
-    <t>13.3633° N, 103.8564° E</t>
-  </si>
-  <si>
-    <t>Indonesia</t>
-  </si>
-  <si>
-    <t>Jakarta</t>
-  </si>
-  <si>
-    <t>6.1944° S, 106.8229° E</t>
-  </si>
-  <si>
-    <t>Oman</t>
-  </si>
-  <si>
-    <t>Muscat</t>
-  </si>
-  <si>
-    <t>23.5880° N, 58.3829° E</t>
   </si>
 </sst>
 </file>
@@ -2053,7 +2005,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2100,15 +2052,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -3163,7 +3106,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F399"/>
+  <dimension ref="A2:F387"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -9851,13 +9794,13 @@
     </row>
     <row r="370" ht="20.05" customHeight="1">
       <c r="A370" t="s" s="9">
-        <v>331</v>
+        <v>578</v>
       </c>
       <c r="B370" t="s" s="9">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C370" t="s" s="10">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D370" s="11">
         <v>46192</v>
@@ -9865,208 +9808,202 @@
       <c r="E370" s="12">
         <v>46192</v>
       </c>
-      <c r="F370" t="s" s="13">
-        <v>580</v>
-      </c>
+      <c r="F370" s="14"/>
     </row>
     <row r="371" ht="20.05" customHeight="1">
       <c r="A371" t="s" s="9">
+        <v>331</v>
+      </c>
+      <c r="B371" t="s" s="9">
         <v>581</v>
       </c>
-      <c r="B371" t="s" s="9">
+      <c r="C371" t="s" s="10">
         <v>582</v>
       </c>
-      <c r="C371" t="s" s="10">
-        <v>583</v>
-      </c>
       <c r="D371" s="11">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="E371" s="12">
-        <v>46192</v>
-      </c>
-      <c r="F371" t="s" s="13">
-        <v>580</v>
-      </c>
+        <v>46195</v>
+      </c>
+      <c r="F371" s="14"/>
     </row>
     <row r="372" ht="20.05" customHeight="1">
       <c r="A372" t="s" s="9">
         <v>331</v>
       </c>
       <c r="B372" t="s" s="9">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C372" t="s" s="10">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D372" s="11">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="E372" s="12">
-        <v>46193</v>
-      </c>
-      <c r="F372" t="s" s="13">
-        <v>580</v>
-      </c>
+        <v>46195</v>
+      </c>
+      <c r="F372" s="14"/>
     </row>
     <row r="373" ht="20.05" customHeight="1">
       <c r="A373" t="s" s="9">
-        <v>331</v>
+        <v>292</v>
       </c>
       <c r="B373" t="s" s="9">
-        <v>584</v>
+        <v>293</v>
       </c>
       <c r="C373" t="s" s="10">
+        <v>294</v>
+      </c>
+      <c r="D373" s="11">
+        <v>46195</v>
+      </c>
+      <c r="E373" s="12">
+        <v>46227</v>
+      </c>
+      <c r="F373" t="s" s="13">
         <v>585</v>
-      </c>
-      <c r="D373" s="11">
-        <v>46193</v>
-      </c>
-      <c r="E373" s="12">
-        <v>46193</v>
-      </c>
-      <c r="F373" t="s" s="13">
-        <v>580</v>
       </c>
     </row>
     <row r="374" ht="20.05" customHeight="1">
       <c r="A374" t="s" s="9">
-        <v>331</v>
+        <v>460</v>
       </c>
       <c r="B374" t="s" s="9">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C374" t="s" s="10">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="D374" s="11">
-        <v>46193</v>
+        <v>46227</v>
       </c>
       <c r="E374" s="12">
-        <v>46194</v>
+        <v>46228</v>
       </c>
       <c r="F374" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="375" ht="20.05" customHeight="1">
       <c r="A375" t="s" s="9">
-        <v>331</v>
+        <v>588</v>
       </c>
       <c r="B375" t="s" s="9">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C375" t="s" s="10">
+        <v>589</v>
+      </c>
+      <c r="D375" s="11">
+        <v>46228</v>
+      </c>
+      <c r="E375" s="12">
+        <v>46228</v>
+      </c>
+      <c r="F375" t="s" s="13">
         <v>585</v>
-      </c>
-      <c r="D375" s="11">
-        <v>46194</v>
-      </c>
-      <c r="E375" s="12">
-        <v>46194</v>
-      </c>
-      <c r="F375" t="s" s="13">
-        <v>580</v>
       </c>
     </row>
     <row r="376" ht="20.05" customHeight="1">
       <c r="A376" t="s" s="9">
-        <v>331</v>
+        <v>460</v>
       </c>
       <c r="B376" t="s" s="9">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C376" t="s" s="10">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="D376" s="11">
-        <v>46194</v>
+        <v>46228</v>
       </c>
       <c r="E376" s="12">
-        <v>46195</v>
+        <v>46229</v>
       </c>
       <c r="F376" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="377" ht="20.05" customHeight="1">
       <c r="A377" t="s" s="9">
-        <v>292</v>
+        <v>590</v>
       </c>
       <c r="B377" t="s" s="9">
-        <v>293</v>
+        <v>591</v>
       </c>
       <c r="C377" t="s" s="10">
-        <v>294</v>
+        <v>592</v>
       </c>
       <c r="D377" s="11">
-        <v>46195</v>
+        <v>46229</v>
       </c>
       <c r="E377" s="12">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="F377" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="378" ht="20.05" customHeight="1">
       <c r="A378" t="s" s="9">
-        <v>460</v>
+        <v>590</v>
       </c>
       <c r="B378" t="s" s="9">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="C378" t="s" s="10">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="D378" s="11">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="E378" s="12">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="F378" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="379" ht="20.05" customHeight="1">
       <c r="A379" t="s" s="9">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B379" t="s" s="9">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="C379" t="s" s="10">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="D379" s="11">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="E379" s="12">
-        <v>46228</v>
+        <v>46232</v>
       </c>
       <c r="F379" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="380" ht="20.05" customHeight="1">
       <c r="A380" t="s" s="9">
-        <v>460</v>
+        <v>590</v>
       </c>
       <c r="B380" t="s" s="9">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="C380" t="s" s="10">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="D380" s="11">
-        <v>46228</v>
+        <v>46232</v>
       </c>
       <c r="E380" s="12">
-        <v>46229</v>
+        <v>46233</v>
       </c>
       <c r="F380" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="381" ht="20.05" customHeight="1">
@@ -10074,19 +10011,19 @@
         <v>590</v>
       </c>
       <c r="B381" t="s" s="9">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C381" t="s" s="10">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="D381" s="11">
-        <v>46229</v>
+        <v>46233</v>
       </c>
       <c r="E381" s="12">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="F381" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="382" ht="20.05" customHeight="1">
@@ -10094,19 +10031,19 @@
         <v>590</v>
       </c>
       <c r="B382" t="s" s="9">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="C382" t="s" s="10">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="D382" s="11">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="E382" s="12">
-        <v>46231</v>
+        <v>46236</v>
       </c>
       <c r="F382" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="383" ht="20.05" customHeight="1">
@@ -10114,19 +10051,19 @@
         <v>590</v>
       </c>
       <c r="B383" t="s" s="9">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="C383" t="s" s="10">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="D383" s="11">
-        <v>46231</v>
+        <v>46236</v>
       </c>
       <c r="E383" s="12">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="F383" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="384" ht="20.05" customHeight="1">
@@ -10134,19 +10071,19 @@
         <v>590</v>
       </c>
       <c r="B384" t="s" s="9">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="C384" t="s" s="10">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="D384" s="11">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="E384" s="12">
-        <v>46233</v>
+        <v>46265</v>
       </c>
       <c r="F384" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="385" ht="20.05" customHeight="1">
@@ -10154,19 +10091,19 @@
         <v>590</v>
       </c>
       <c r="B385" t="s" s="9">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="C385" t="s" s="10">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="D385" s="11">
-        <v>46233</v>
+        <v>46265</v>
       </c>
       <c r="E385" s="12">
-        <v>46234</v>
+        <v>46267</v>
       </c>
       <c r="F385" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="386" ht="20.05" customHeight="1">
@@ -10174,268 +10111,40 @@
         <v>590</v>
       </c>
       <c r="B386" t="s" s="9">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="C386" t="s" s="10">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="D386" s="11">
-        <v>46234</v>
+        <v>46267</v>
       </c>
       <c r="E386" s="12">
-        <v>46236</v>
+        <v>46270</v>
       </c>
       <c r="F386" t="s" s="13">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="387" ht="20.05" customHeight="1">
       <c r="A387" t="s" s="9">
-        <v>590</v>
+        <v>292</v>
       </c>
       <c r="B387" t="s" s="9">
-        <v>603</v>
+        <v>293</v>
       </c>
       <c r="C387" t="s" s="10">
-        <v>604</v>
+        <v>294</v>
       </c>
       <c r="D387" s="11">
-        <v>46236</v>
+        <v>46270</v>
       </c>
       <c r="E387" s="12">
-        <v>46263</v>
+        <v>46271</v>
       </c>
       <c r="F387" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="388" ht="20.05" customHeight="1">
-      <c r="A388" t="s" s="9">
-        <v>590</v>
-      </c>
-      <c r="B388" t="s" s="9">
-        <v>605</v>
-      </c>
-      <c r="C388" t="s" s="10">
-        <v>606</v>
-      </c>
-      <c r="D388" s="11">
-        <v>46263</v>
-      </c>
-      <c r="E388" s="12">
-        <v>46265</v>
-      </c>
-      <c r="F388" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="389" ht="20.05" customHeight="1">
-      <c r="A389" t="s" s="9">
-        <v>590</v>
-      </c>
-      <c r="B389" t="s" s="9">
-        <v>607</v>
-      </c>
-      <c r="C389" t="s" s="10">
-        <v>608</v>
-      </c>
-      <c r="D389" s="11">
-        <v>46265</v>
-      </c>
-      <c r="E389" s="12">
-        <v>46267</v>
-      </c>
-      <c r="F389" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="390" ht="20.05" customHeight="1">
-      <c r="A390" t="s" s="9">
-        <v>590</v>
-      </c>
-      <c r="B390" t="s" s="9">
-        <v>609</v>
-      </c>
-      <c r="C390" t="s" s="10">
-        <v>610</v>
-      </c>
-      <c r="D390" s="11">
-        <v>46267</v>
-      </c>
-      <c r="E390" s="12">
-        <v>46270</v>
-      </c>
-      <c r="F390" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="391" ht="20.05" customHeight="1">
-      <c r="A391" t="s" s="9">
-        <v>292</v>
-      </c>
-      <c r="B391" t="s" s="9">
-        <v>293</v>
-      </c>
-      <c r="C391" t="s" s="10">
-        <v>294</v>
-      </c>
-      <c r="D391" s="11">
-        <v>46270</v>
-      </c>
-      <c r="E391" s="12">
-        <v>46373</v>
-      </c>
-      <c r="F391" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="392" ht="20.05" customHeight="1">
-      <c r="A392" t="s" s="9">
-        <v>611</v>
-      </c>
-      <c r="B392" t="s" s="9">
-        <v>612</v>
-      </c>
-      <c r="C392" t="s" s="10">
-        <v>613</v>
-      </c>
-      <c r="D392" s="11">
-        <v>46373</v>
-      </c>
-      <c r="E392" s="12">
-        <v>46380</v>
-      </c>
-      <c r="F392" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="393" ht="20.05" customHeight="1">
-      <c r="A393" t="s" s="9">
-        <v>611</v>
-      </c>
-      <c r="B393" t="s" s="9">
-        <v>614</v>
-      </c>
-      <c r="C393" t="s" s="10">
-        <v>615</v>
-      </c>
-      <c r="D393" s="11">
-        <v>46380</v>
-      </c>
-      <c r="E393" s="12">
-        <v>46385</v>
-      </c>
-      <c r="F393" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="394" ht="20.05" customHeight="1">
-      <c r="A394" t="s" s="9">
-        <v>616</v>
-      </c>
-      <c r="B394" t="s" s="9">
-        <v>617</v>
-      </c>
-      <c r="C394" t="s" s="10">
-        <v>618</v>
-      </c>
-      <c r="D394" s="11">
-        <v>46385</v>
-      </c>
-      <c r="E394" s="12">
-        <v>46388</v>
-      </c>
-      <c r="F394" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="395" ht="20.05" customHeight="1">
-      <c r="A395" t="s" s="9">
-        <v>616</v>
-      </c>
-      <c r="B395" t="s" s="9">
-        <v>619</v>
-      </c>
-      <c r="C395" t="s" s="10">
-        <v>620</v>
-      </c>
-      <c r="D395" s="11">
-        <v>46388</v>
-      </c>
-      <c r="E395" s="12">
-        <v>46390</v>
-      </c>
-      <c r="F395" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="396" ht="20.05" customHeight="1">
-      <c r="A396" t="s" s="9">
-        <v>621</v>
-      </c>
-      <c r="B396" t="s" s="9">
-        <v>622</v>
-      </c>
-      <c r="C396" t="s" s="10">
-        <v>623</v>
-      </c>
-      <c r="D396" s="11">
-        <v>46390</v>
-      </c>
-      <c r="E396" s="12">
-        <v>46393</v>
-      </c>
-      <c r="F396" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="397" ht="20.05" customHeight="1">
-      <c r="A397" t="s" s="9">
-        <v>624</v>
-      </c>
-      <c r="B397" t="s" s="9">
-        <v>625</v>
-      </c>
-      <c r="C397" t="s" s="10">
-        <v>626</v>
-      </c>
-      <c r="D397" s="11">
-        <v>46393</v>
-      </c>
-      <c r="E397" s="12">
-        <v>46396</v>
-      </c>
-      <c r="F397" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="398" ht="20.05" customHeight="1">
-      <c r="A398" t="s" s="9">
-        <v>292</v>
-      </c>
-      <c r="B398" t="s" s="9">
-        <v>293</v>
-      </c>
-      <c r="C398" t="s" s="10">
-        <v>294</v>
-      </c>
-      <c r="D398" s="11">
-        <v>46396</v>
-      </c>
-      <c r="E398" s="12">
-        <v>46418</v>
-      </c>
-      <c r="F398" t="s" s="13">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="399" ht="20.05" customHeight="1">
-      <c r="A399" s="16"/>
-      <c r="B399" s="16"/>
-      <c r="C399" s="17"/>
-      <c r="D399" s="18"/>
-      <c r="E399" s="14"/>
-      <c r="F399" s="14"/>
+        <v>585</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="618">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1783,67 +1783,88 @@
     <t>43.7384° N, 7.4246° E</t>
   </si>
   <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t>43.3026° N, 5.3691° E</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>Dakar</t>
+  </si>
+  <si>
+    <t>14.7167° N, 17.4677° W</t>
+  </si>
+  <si>
     <t>Morocco</t>
   </si>
   <si>
+    <t>Casablanca</t>
+  </si>
+  <si>
+    <t>33.5731° N, 7.5898° W</t>
+  </si>
+  <si>
+    <t>Ouarzazate</t>
+  </si>
+  <si>
+    <t>30.9335° N, 6.9370° W</t>
+  </si>
+  <si>
+    <t>Aït Benhaddou</t>
+  </si>
+  <si>
+    <t>31.0470° N, 7.1319° W</t>
+  </si>
+  <si>
+    <t>Rabat</t>
+  </si>
+  <si>
+    <t>34.0084° N, 6.8539° W</t>
+  </si>
+  <si>
+    <t>Marrakesh</t>
+  </si>
+  <si>
+    <t>31.6225° N, 7.9898° W</t>
+  </si>
+  <si>
+    <t>Meknes</t>
+  </si>
+  <si>
+    <t>33.8675° N, 5.5382° W</t>
+  </si>
+  <si>
+    <t>Fes</t>
+  </si>
+  <si>
+    <t>34.0181° N, 5.0078° W</t>
+  </si>
+  <si>
+    <t>Tetouan</t>
+  </si>
+  <si>
+    <t>35.5717° N, 5.3597° W</t>
+  </si>
+  <si>
+    <t>Chefchaouen</t>
+  </si>
+  <si>
+    <t>35.1688° N, 5.2684° W</t>
+  </si>
+  <si>
     <t>Tangier</t>
   </si>
   <si>
     <t>35.7595° N, 5.8340° W</t>
   </si>
   <si>
-    <t>Tetouan</t>
-  </si>
-  <si>
-    <t>35.5717° N, 5.3597° W</t>
-  </si>
-  <si>
-    <t>Chefchaouen</t>
-  </si>
-  <si>
-    <t>35.1688° N, 5.2684° W</t>
-  </si>
-  <si>
-    <t>Fes</t>
-  </si>
-  <si>
-    <t>34.0181° N, 5.0078° W</t>
-  </si>
-  <si>
-    <t>Meknes</t>
-  </si>
-  <si>
-    <t>33.8675° N, 5.5382° W</t>
-  </si>
-  <si>
-    <t>Rabat</t>
-  </si>
-  <si>
-    <t>34.0084° N, 6.8539° W</t>
-  </si>
-  <si>
-    <t>Casablanca</t>
-  </si>
-  <si>
-    <t>33.5731° N, 7.5898° W</t>
-  </si>
-  <si>
-    <t>Ouarzazate</t>
-  </si>
-  <si>
-    <t>30.9335° N, 6.9370° W</t>
-  </si>
-  <si>
-    <t>Aït Benhaddou</t>
-  </si>
-  <si>
-    <t>31.0470° N, 7.1319° W</t>
-  </si>
-  <si>
-    <t>Marrakesh</t>
-  </si>
-  <si>
-    <t>31.6225° N, 7.9898° W</t>
+    <t>Malaga</t>
+  </si>
+  <si>
+    <t>36.7178° N, 4.4256° W</t>
   </si>
 </sst>
 </file>
@@ -3106,7 +3127,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F387"/>
+  <dimension ref="A2:F394"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -9740,34 +9761,34 @@
     </row>
     <row r="367" ht="20.05" customHeight="1">
       <c r="A367" t="s" s="9">
-        <v>483</v>
+        <v>324</v>
       </c>
       <c r="B367" t="s" s="9">
-        <v>574</v>
+        <v>325</v>
       </c>
       <c r="C367" t="s" s="10">
-        <v>575</v>
+        <v>326</v>
       </c>
       <c r="D367" s="11">
         <v>46172</v>
       </c>
       <c r="E367" s="12">
-        <v>46179</v>
+        <v>46172</v>
       </c>
       <c r="F367" s="14"/>
     </row>
     <row r="368" ht="20.05" customHeight="1">
       <c r="A368" t="s" s="9">
-        <v>331</v>
+        <v>483</v>
       </c>
       <c r="B368" t="s" s="9">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C368" t="s" s="10">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D368" s="11">
-        <v>46179</v>
+        <v>46172</v>
       </c>
       <c r="E368" s="12">
         <v>46179</v>
@@ -9776,34 +9797,34 @@
     </row>
     <row r="369" ht="20.05" customHeight="1">
       <c r="A369" t="s" s="9">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="B369" t="s" s="9">
-        <v>293</v>
+        <v>576</v>
       </c>
       <c r="C369" t="s" s="10">
-        <v>294</v>
+        <v>577</v>
       </c>
       <c r="D369" s="11">
         <v>46179</v>
       </c>
       <c r="E369" s="12">
-        <v>46192</v>
+        <v>46179</v>
       </c>
       <c r="F369" s="14"/>
     </row>
     <row r="370" ht="20.05" customHeight="1">
       <c r="A370" t="s" s="9">
-        <v>578</v>
+        <v>292</v>
       </c>
       <c r="B370" t="s" s="9">
-        <v>579</v>
+        <v>293</v>
       </c>
       <c r="C370" t="s" s="10">
-        <v>580</v>
+        <v>294</v>
       </c>
       <c r="D370" s="11">
-        <v>46192</v>
+        <v>46179</v>
       </c>
       <c r="E370" s="12">
         <v>46192</v>
@@ -9812,19 +9833,19 @@
     </row>
     <row r="371" ht="20.05" customHeight="1">
       <c r="A371" t="s" s="9">
-        <v>331</v>
+        <v>578</v>
       </c>
       <c r="B371" t="s" s="9">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C371" t="s" s="10">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D371" s="11">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="E371" s="12">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="F371" s="14"/>
     </row>
@@ -9833,13 +9854,13 @@
         <v>331</v>
       </c>
       <c r="B372" t="s" s="9">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C372" t="s" s="10">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D372" s="11">
-        <v>46195</v>
+        <v>46193</v>
       </c>
       <c r="E372" s="12">
         <v>46195</v>
@@ -9848,39 +9869,37 @@
     </row>
     <row r="373" ht="20.05" customHeight="1">
       <c r="A373" t="s" s="9">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="B373" t="s" s="9">
-        <v>293</v>
+        <v>583</v>
       </c>
       <c r="C373" t="s" s="10">
-        <v>294</v>
+        <v>584</v>
       </c>
       <c r="D373" s="11">
         <v>46195</v>
       </c>
       <c r="E373" s="12">
-        <v>46227</v>
-      </c>
-      <c r="F373" t="s" s="13">
-        <v>585</v>
-      </c>
+        <v>46195</v>
+      </c>
+      <c r="F373" s="14"/>
     </row>
     <row r="374" ht="20.05" customHeight="1">
       <c r="A374" t="s" s="9">
-        <v>460</v>
+        <v>292</v>
       </c>
       <c r="B374" t="s" s="9">
-        <v>586</v>
+        <v>293</v>
       </c>
       <c r="C374" t="s" s="10">
-        <v>587</v>
+        <v>294</v>
       </c>
       <c r="D374" s="11">
+        <v>46195</v>
+      </c>
+      <c r="E374" s="12">
         <v>46227</v>
-      </c>
-      <c r="E374" s="12">
-        <v>46228</v>
       </c>
       <c r="F374" t="s" s="13">
         <v>585</v>
@@ -9888,16 +9907,16 @@
     </row>
     <row r="375" ht="20.05" customHeight="1">
       <c r="A375" t="s" s="9">
-        <v>588</v>
+        <v>460</v>
       </c>
       <c r="B375" t="s" s="9">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C375" t="s" s="10">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D375" s="11">
-        <v>46228</v>
+        <v>46227</v>
       </c>
       <c r="E375" s="12">
         <v>46228</v>
@@ -9908,19 +9927,19 @@
     </row>
     <row r="376" ht="20.05" customHeight="1">
       <c r="A376" t="s" s="9">
-        <v>460</v>
+        <v>588</v>
       </c>
       <c r="B376" t="s" s="9">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C376" t="s" s="10">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D376" s="11">
         <v>46228</v>
       </c>
       <c r="E376" s="12">
-        <v>46229</v>
+        <v>46228</v>
       </c>
       <c r="F376" t="s" s="13">
         <v>585</v>
@@ -9928,19 +9947,19 @@
     </row>
     <row r="377" ht="20.05" customHeight="1">
       <c r="A377" t="s" s="9">
-        <v>590</v>
+        <v>460</v>
       </c>
       <c r="B377" t="s" s="9">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C377" t="s" s="10">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="D377" s="11">
-        <v>46229</v>
+        <v>46228</v>
       </c>
       <c r="E377" s="12">
-        <v>46230</v>
+        <v>46228</v>
       </c>
       <c r="F377" t="s" s="13">
         <v>585</v>
@@ -9948,19 +9967,19 @@
     </row>
     <row r="378" ht="20.05" customHeight="1">
       <c r="A378" t="s" s="9">
+        <v>460</v>
+      </c>
+      <c r="B378" t="s" s="9">
         <v>590</v>
       </c>
-      <c r="B378" t="s" s="9">
-        <v>593</v>
-      </c>
       <c r="C378" t="s" s="10">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D378" s="11">
-        <v>46230</v>
+        <v>46228</v>
       </c>
       <c r="E378" s="12">
-        <v>46231</v>
+        <v>46229</v>
       </c>
       <c r="F378" t="s" s="13">
         <v>585</v>
@@ -9968,16 +9987,16 @@
     </row>
     <row r="379" ht="20.05" customHeight="1">
       <c r="A379" t="s" s="9">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B379" t="s" s="9">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C379" t="s" s="10">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D379" s="11">
-        <v>46231</v>
+        <v>46229</v>
       </c>
       <c r="E379" s="12">
         <v>46232</v>
@@ -9988,19 +10007,19 @@
     </row>
     <row r="380" ht="20.05" customHeight="1">
       <c r="A380" t="s" s="9">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B380" t="s" s="9">
+        <v>596</v>
+      </c>
+      <c r="C380" t="s" s="10">
         <v>597</v>
-      </c>
-      <c r="C380" t="s" s="10">
-        <v>598</v>
       </c>
       <c r="D380" s="11">
         <v>46232</v>
       </c>
       <c r="E380" s="12">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="F380" t="s" s="13">
         <v>585</v>
@@ -10008,16 +10027,16 @@
     </row>
     <row r="381" ht="20.05" customHeight="1">
       <c r="A381" t="s" s="9">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B381" t="s" s="9">
+        <v>598</v>
+      </c>
+      <c r="C381" t="s" s="10">
         <v>599</v>
       </c>
-      <c r="C381" t="s" s="10">
-        <v>600</v>
-      </c>
       <c r="D381" s="11">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="E381" s="12">
         <v>46234</v>
@@ -10028,13 +10047,13 @@
     </row>
     <row r="382" ht="20.05" customHeight="1">
       <c r="A382" t="s" s="9">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B382" t="s" s="9">
+        <v>600</v>
+      </c>
+      <c r="C382" t="s" s="10">
         <v>601</v>
-      </c>
-      <c r="C382" t="s" s="10">
-        <v>602</v>
       </c>
       <c r="D382" s="11">
         <v>46234</v>
@@ -10048,19 +10067,19 @@
     </row>
     <row r="383" ht="20.05" customHeight="1">
       <c r="A383" t="s" s="9">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B383" t="s" s="9">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="C383" t="s" s="10">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="D383" s="11">
         <v>46236</v>
       </c>
       <c r="E383" s="12">
-        <v>46263</v>
+        <v>46249</v>
       </c>
       <c r="F383" t="s" s="13">
         <v>585</v>
@@ -10068,19 +10087,19 @@
     </row>
     <row r="384" ht="20.05" customHeight="1">
       <c r="A384" t="s" s="9">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B384" t="s" s="9">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C384" t="s" s="10">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D384" s="11">
-        <v>46263</v>
+        <v>46249</v>
       </c>
       <c r="E384" s="12">
-        <v>46265</v>
+        <v>46250</v>
       </c>
       <c r="F384" t="s" s="13">
         <v>585</v>
@@ -10088,19 +10107,19 @@
     </row>
     <row r="385" ht="20.05" customHeight="1">
       <c r="A385" t="s" s="9">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B385" t="s" s="9">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="C385" t="s" s="10">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="D385" s="11">
-        <v>46265</v>
+        <v>46250</v>
       </c>
       <c r="E385" s="12">
-        <v>46267</v>
+        <v>46256</v>
       </c>
       <c r="F385" t="s" s="13">
         <v>585</v>
@@ -10108,19 +10127,19 @@
     </row>
     <row r="386" ht="20.05" customHeight="1">
       <c r="A386" t="s" s="9">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B386" t="s" s="9">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C386" t="s" s="10">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D386" s="11">
-        <v>46267</v>
+        <v>46256</v>
       </c>
       <c r="E386" s="12">
-        <v>46270</v>
+        <v>46257</v>
       </c>
       <c r="F386" t="s" s="13">
         <v>585</v>
@@ -10128,21 +10147,161 @@
     </row>
     <row r="387" ht="20.05" customHeight="1">
       <c r="A387" t="s" s="9">
+        <v>595</v>
+      </c>
+      <c r="B387" t="s" s="9">
+        <v>596</v>
+      </c>
+      <c r="C387" t="s" s="10">
+        <v>597</v>
+      </c>
+      <c r="D387" s="11">
+        <v>46257</v>
+      </c>
+      <c r="E387" s="12">
+        <v>46264</v>
+      </c>
+      <c r="F387" t="s" s="13">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="388" ht="20.05" customHeight="1">
+      <c r="A388" t="s" s="9">
+        <v>595</v>
+      </c>
+      <c r="B388" t="s" s="9">
+        <v>606</v>
+      </c>
+      <c r="C388" t="s" s="10">
+        <v>607</v>
+      </c>
+      <c r="D388" s="11">
+        <v>46264</v>
+      </c>
+      <c r="E388" s="12">
+        <v>46265</v>
+      </c>
+      <c r="F388" t="s" s="13">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="389" ht="20.05" customHeight="1">
+      <c r="A389" t="s" s="9">
+        <v>595</v>
+      </c>
+      <c r="B389" t="s" s="9">
+        <v>608</v>
+      </c>
+      <c r="C389" t="s" s="10">
+        <v>609</v>
+      </c>
+      <c r="D389" s="11">
+        <v>46265</v>
+      </c>
+      <c r="E389" s="12">
+        <v>46266</v>
+      </c>
+      <c r="F389" t="s" s="13">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="390" ht="20.05" customHeight="1">
+      <c r="A390" t="s" s="9">
+        <v>595</v>
+      </c>
+      <c r="B390" t="s" s="9">
+        <v>610</v>
+      </c>
+      <c r="C390" t="s" s="10">
+        <v>611</v>
+      </c>
+      <c r="D390" s="11">
+        <v>46266</v>
+      </c>
+      <c r="E390" s="12">
+        <v>46267</v>
+      </c>
+      <c r="F390" t="s" s="13">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="391" ht="20.05" customHeight="1">
+      <c r="A391" t="s" s="9">
+        <v>595</v>
+      </c>
+      <c r="B391" t="s" s="9">
+        <v>612</v>
+      </c>
+      <c r="C391" t="s" s="10">
+        <v>613</v>
+      </c>
+      <c r="D391" s="11">
+        <v>46267</v>
+      </c>
+      <c r="E391" s="12">
+        <v>46268</v>
+      </c>
+      <c r="F391" t="s" s="13">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="392" ht="20.05" customHeight="1">
+      <c r="A392" t="s" s="9">
+        <v>595</v>
+      </c>
+      <c r="B392" t="s" s="9">
+        <v>614</v>
+      </c>
+      <c r="C392" t="s" s="10">
+        <v>615</v>
+      </c>
+      <c r="D392" s="11">
+        <v>46268</v>
+      </c>
+      <c r="E392" s="12">
+        <v>46270</v>
+      </c>
+      <c r="F392" t="s" s="13">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="393" ht="20.05" customHeight="1">
+      <c r="A393" t="s" s="9">
+        <v>502</v>
+      </c>
+      <c r="B393" t="s" s="9">
+        <v>616</v>
+      </c>
+      <c r="C393" t="s" s="10">
+        <v>617</v>
+      </c>
+      <c r="D393" s="11">
+        <v>46270</v>
+      </c>
+      <c r="E393" s="12">
+        <v>46270</v>
+      </c>
+      <c r="F393" t="s" s="13">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="394" ht="20.05" customHeight="1">
+      <c r="A394" t="s" s="9">
         <v>292</v>
       </c>
-      <c r="B387" t="s" s="9">
+      <c r="B394" t="s" s="9">
         <v>293</v>
       </c>
-      <c r="C387" t="s" s="10">
+      <c r="C394" t="s" s="10">
         <v>294</v>
       </c>
-      <c r="D387" s="11">
+      <c r="D394" s="11">
         <v>46270</v>
       </c>
-      <c r="E387" s="12">
+      <c r="E394" s="12">
         <v>46271</v>
       </c>
-      <c r="F387" t="s" s="13">
+      <c r="F394" t="s" s="13">
         <v>585</v>
       </c>
     </row>

--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="615">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1789,34 +1789,25 @@
     <t>43.3026° N, 5.3691° E</t>
   </si>
   <si>
-    <t>Senegal</t>
-  </si>
-  <si>
-    <t>Dakar</t>
-  </si>
-  <si>
-    <t>14.7167° N, 17.4677° W</t>
-  </si>
-  <si>
     <t>Morocco</t>
   </si>
   <si>
+    <t>Ouarzazate</t>
+  </si>
+  <si>
+    <t>30.9335° N, 6.9370° W</t>
+  </si>
+  <si>
+    <t>Aït Benhaddou</t>
+  </si>
+  <si>
+    <t>31.0470° N, 7.1319° W</t>
+  </si>
+  <si>
     <t>Casablanca</t>
   </si>
   <si>
     <t>33.5731° N, 7.5898° W</t>
-  </si>
-  <si>
-    <t>Ouarzazate</t>
-  </si>
-  <si>
-    <t>30.9335° N, 6.9370° W</t>
-  </si>
-  <si>
-    <t>Aït Benhaddou</t>
-  </si>
-  <si>
-    <t>31.0470° N, 7.1319° W</t>
   </si>
   <si>
     <t>Rabat</t>
@@ -3127,7 +3118,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F394"/>
+  <dimension ref="A2:F392"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -9899,7 +9890,7 @@
         <v>46195</v>
       </c>
       <c r="E374" s="12">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="F374" t="s" s="13">
         <v>585</v>
@@ -9916,10 +9907,10 @@
         <v>587</v>
       </c>
       <c r="D375" s="11">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="E375" s="12">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="F375" t="s" s="13">
         <v>585</v>
@@ -9936,10 +9927,10 @@
         <v>589</v>
       </c>
       <c r="D376" s="11">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="E376" s="12">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="F376" t="s" s="13">
         <v>585</v>
@@ -9956,10 +9947,10 @@
         <v>587</v>
       </c>
       <c r="D377" s="11">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="E377" s="12">
-        <v>46228</v>
+        <v>46226</v>
       </c>
       <c r="F377" t="s" s="13">
         <v>585</v>
@@ -9976,10 +9967,10 @@
         <v>591</v>
       </c>
       <c r="D378" s="11">
-        <v>46228</v>
+        <v>46226</v>
       </c>
       <c r="E378" s="12">
-        <v>46229</v>
+        <v>46227</v>
       </c>
       <c r="F378" t="s" s="13">
         <v>585</v>
@@ -9996,10 +9987,10 @@
         <v>594</v>
       </c>
       <c r="D379" s="11">
-        <v>46229</v>
+        <v>46227</v>
       </c>
       <c r="E379" s="12">
-        <v>46232</v>
+        <v>46228</v>
       </c>
       <c r="F379" t="s" s="13">
         <v>585</v>
@@ -10007,19 +9998,19 @@
     </row>
     <row r="380" ht="20.05" customHeight="1">
       <c r="A380" t="s" s="9">
+        <v>592</v>
+      </c>
+      <c r="B380" t="s" s="9">
         <v>595</v>
       </c>
-      <c r="B380" t="s" s="9">
+      <c r="C380" t="s" s="10">
         <v>596</v>
       </c>
-      <c r="C380" t="s" s="10">
-        <v>597</v>
-      </c>
       <c r="D380" s="11">
-        <v>46232</v>
+        <v>46228</v>
       </c>
       <c r="E380" s="12">
-        <v>46232</v>
+        <v>46229</v>
       </c>
       <c r="F380" t="s" s="13">
         <v>585</v>
@@ -10027,19 +10018,19 @@
     </row>
     <row r="381" ht="20.05" customHeight="1">
       <c r="A381" t="s" s="9">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B381" t="s" s="9">
+        <v>597</v>
+      </c>
+      <c r="C381" t="s" s="10">
         <v>598</v>
       </c>
-      <c r="C381" t="s" s="10">
-        <v>599</v>
-      </c>
       <c r="D381" s="11">
-        <v>46232</v>
+        <v>46229</v>
       </c>
       <c r="E381" s="12">
-        <v>46234</v>
+        <v>46249</v>
       </c>
       <c r="F381" t="s" s="13">
         <v>585</v>
@@ -10047,19 +10038,19 @@
     </row>
     <row r="382" ht="20.05" customHeight="1">
       <c r="A382" t="s" s="9">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B382" t="s" s="9">
+        <v>599</v>
+      </c>
+      <c r="C382" t="s" s="10">
         <v>600</v>
       </c>
-      <c r="C382" t="s" s="10">
-        <v>601</v>
-      </c>
       <c r="D382" s="11">
-        <v>46234</v>
+        <v>46249</v>
       </c>
       <c r="E382" s="12">
-        <v>46236</v>
+        <v>46250</v>
       </c>
       <c r="F382" t="s" s="13">
         <v>585</v>
@@ -10067,19 +10058,19 @@
     </row>
     <row r="383" ht="20.05" customHeight="1">
       <c r="A383" t="s" s="9">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B383" t="s" s="9">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C383" t="s" s="10">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D383" s="11">
-        <v>46236</v>
+        <v>46250</v>
       </c>
       <c r="E383" s="12">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="F383" t="s" s="13">
         <v>585</v>
@@ -10087,19 +10078,19 @@
     </row>
     <row r="384" ht="20.05" customHeight="1">
       <c r="A384" t="s" s="9">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B384" t="s" s="9">
+        <v>601</v>
+      </c>
+      <c r="C384" t="s" s="10">
         <v>602</v>
       </c>
-      <c r="C384" t="s" s="10">
-        <v>603</v>
-      </c>
       <c r="D384" s="11">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="E384" s="12">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="F384" t="s" s="13">
         <v>585</v>
@@ -10107,19 +10098,19 @@
     </row>
     <row r="385" ht="20.05" customHeight="1">
       <c r="A385" t="s" s="9">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B385" t="s" s="9">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C385" t="s" s="10">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D385" s="11">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="E385" s="12">
-        <v>46256</v>
+        <v>46264</v>
       </c>
       <c r="F385" t="s" s="13">
         <v>585</v>
@@ -10127,19 +10118,19 @@
     </row>
     <row r="386" ht="20.05" customHeight="1">
       <c r="A386" t="s" s="9">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B386" t="s" s="9">
+        <v>603</v>
+      </c>
+      <c r="C386" t="s" s="10">
         <v>604</v>
       </c>
-      <c r="C386" t="s" s="10">
-        <v>605</v>
-      </c>
       <c r="D386" s="11">
-        <v>46256</v>
+        <v>46264</v>
       </c>
       <c r="E386" s="12">
-        <v>46257</v>
+        <v>46265</v>
       </c>
       <c r="F386" t="s" s="13">
         <v>585</v>
@@ -10147,19 +10138,19 @@
     </row>
     <row r="387" ht="20.05" customHeight="1">
       <c r="A387" t="s" s="9">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B387" t="s" s="9">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="C387" t="s" s="10">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="D387" s="11">
-        <v>46257</v>
+        <v>46265</v>
       </c>
       <c r="E387" s="12">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="F387" t="s" s="13">
         <v>585</v>
@@ -10167,19 +10158,19 @@
     </row>
     <row r="388" ht="20.05" customHeight="1">
       <c r="A388" t="s" s="9">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B388" t="s" s="9">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C388" t="s" s="10">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D388" s="11">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="E388" s="12">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="F388" t="s" s="13">
         <v>585</v>
@@ -10187,19 +10178,19 @@
     </row>
     <row r="389" ht="20.05" customHeight="1">
       <c r="A389" t="s" s="9">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B389" t="s" s="9">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C389" t="s" s="10">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D389" s="11">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="E389" s="12">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="F389" t="s" s="13">
         <v>585</v>
@@ -10207,19 +10198,19 @@
     </row>
     <row r="390" ht="20.05" customHeight="1">
       <c r="A390" t="s" s="9">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B390" t="s" s="9">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C390" t="s" s="10">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D390" s="11">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="E390" s="12">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="F390" t="s" s="13">
         <v>585</v>
@@ -10227,19 +10218,19 @@
     </row>
     <row r="391" ht="20.05" customHeight="1">
       <c r="A391" t="s" s="9">
-        <v>595</v>
+        <v>502</v>
       </c>
       <c r="B391" t="s" s="9">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C391" t="s" s="10">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D391" s="11">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="E391" s="12">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="F391" t="s" s="13">
         <v>585</v>
@@ -10247,61 +10238,21 @@
     </row>
     <row r="392" ht="20.05" customHeight="1">
       <c r="A392" t="s" s="9">
-        <v>595</v>
+        <v>292</v>
       </c>
       <c r="B392" t="s" s="9">
-        <v>614</v>
+        <v>293</v>
       </c>
       <c r="C392" t="s" s="10">
-        <v>615</v>
+        <v>294</v>
       </c>
       <c r="D392" s="11">
-        <v>46268</v>
+        <v>46270</v>
       </c>
       <c r="E392" s="12">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="F392" t="s" s="13">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="393" ht="20.05" customHeight="1">
-      <c r="A393" t="s" s="9">
-        <v>502</v>
-      </c>
-      <c r="B393" t="s" s="9">
-        <v>616</v>
-      </c>
-      <c r="C393" t="s" s="10">
-        <v>617</v>
-      </c>
-      <c r="D393" s="11">
-        <v>46270</v>
-      </c>
-      <c r="E393" s="12">
-        <v>46270</v>
-      </c>
-      <c r="F393" t="s" s="13">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="394" ht="20.05" customHeight="1">
-      <c r="A394" t="s" s="9">
-        <v>292</v>
-      </c>
-      <c r="B394" t="s" s="9">
-        <v>293</v>
-      </c>
-      <c r="C394" t="s" s="10">
-        <v>294</v>
-      </c>
-      <c r="D394" s="11">
-        <v>46270</v>
-      </c>
-      <c r="E394" s="12">
-        <v>46271</v>
-      </c>
-      <c r="F394" t="s" s="13">
         <v>585</v>
       </c>
     </row>

--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="617">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1852,10 +1852,16 @@
     <t>35.7595° N, 5.8340° W</t>
   </si>
   <si>
-    <t>Malaga</t>
-  </si>
-  <si>
-    <t>36.7178° N, 4.4256° W</t>
+    <t>Valencia</t>
+  </si>
+  <si>
+    <t>39.4738° N, 0.3756° W</t>
+  </si>
+  <si>
+    <t>Alicante</t>
+  </si>
+  <si>
+    <t>38.3458° N, 0.4909° W</t>
   </si>
 </sst>
 </file>
@@ -3118,7 +3124,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F392"/>
+  <dimension ref="A2:F393"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -10030,7 +10036,7 @@
         <v>46229</v>
       </c>
       <c r="E381" s="12">
-        <v>46249</v>
+        <v>46241</v>
       </c>
       <c r="F381" t="s" s="13">
         <v>585</v>
@@ -10047,10 +10053,10 @@
         <v>600</v>
       </c>
       <c r="D382" s="11">
-        <v>46249</v>
+        <v>46241</v>
       </c>
       <c r="E382" s="12">
-        <v>46250</v>
+        <v>46243</v>
       </c>
       <c r="F382" t="s" s="13">
         <v>585</v>
@@ -10067,10 +10073,10 @@
         <v>598</v>
       </c>
       <c r="D383" s="11">
-        <v>46250</v>
+        <v>46243</v>
       </c>
       <c r="E383" s="12">
-        <v>46256</v>
+        <v>46248</v>
       </c>
       <c r="F383" t="s" s="13">
         <v>585</v>
@@ -10087,10 +10093,10 @@
         <v>602</v>
       </c>
       <c r="D384" s="11">
-        <v>46256</v>
+        <v>46248</v>
       </c>
       <c r="E384" s="12">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="F384" t="s" s="13">
         <v>585</v>
@@ -10107,10 +10113,10 @@
         <v>598</v>
       </c>
       <c r="D385" s="11">
-        <v>46257</v>
+        <v>46250</v>
       </c>
       <c r="E385" s="12">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="F385" t="s" s="13">
         <v>585</v>
@@ -10127,10 +10133,10 @@
         <v>604</v>
       </c>
       <c r="D386" s="11">
+        <v>46263</v>
+      </c>
+      <c r="E386" s="12">
         <v>46264</v>
-      </c>
-      <c r="E386" s="12">
-        <v>46265</v>
       </c>
       <c r="F386" t="s" s="13">
         <v>585</v>
@@ -10147,10 +10153,10 @@
         <v>606</v>
       </c>
       <c r="D387" s="11">
+        <v>46264</v>
+      </c>
+      <c r="E387" s="12">
         <v>46265</v>
-      </c>
-      <c r="E387" s="12">
-        <v>46266</v>
       </c>
       <c r="F387" t="s" s="13">
         <v>585</v>
@@ -10167,10 +10173,10 @@
         <v>608</v>
       </c>
       <c r="D388" s="11">
+        <v>46265</v>
+      </c>
+      <c r="E388" s="12">
         <v>46266</v>
-      </c>
-      <c r="E388" s="12">
-        <v>46267</v>
       </c>
       <c r="F388" t="s" s="13">
         <v>585</v>
@@ -10187,10 +10193,10 @@
         <v>610</v>
       </c>
       <c r="D389" s="11">
+        <v>46266</v>
+      </c>
+      <c r="E389" s="12">
         <v>46267</v>
-      </c>
-      <c r="E389" s="12">
-        <v>46268</v>
       </c>
       <c r="F389" t="s" s="13">
         <v>585</v>
@@ -10207,10 +10213,10 @@
         <v>612</v>
       </c>
       <c r="D390" s="11">
+        <v>46267</v>
+      </c>
+      <c r="E390" s="12">
         <v>46268</v>
-      </c>
-      <c r="E390" s="12">
-        <v>46270</v>
       </c>
       <c r="F390" t="s" s="13">
         <v>585</v>
@@ -10227,10 +10233,10 @@
         <v>614</v>
       </c>
       <c r="D391" s="11">
-        <v>46270</v>
+        <v>46268</v>
       </c>
       <c r="E391" s="12">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="F391" t="s" s="13">
         <v>585</v>
@@ -10238,21 +10244,41 @@
     </row>
     <row r="392" ht="20.05" customHeight="1">
       <c r="A392" t="s" s="9">
-        <v>292</v>
+        <v>502</v>
       </c>
       <c r="B392" t="s" s="9">
-        <v>293</v>
+        <v>615</v>
       </c>
       <c r="C392" t="s" s="10">
-        <v>294</v>
+        <v>616</v>
       </c>
       <c r="D392" s="11">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="E392" s="12">
         <v>46271</v>
       </c>
       <c r="F392" t="s" s="13">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="393" ht="20.05" customHeight="1">
+      <c r="A393" t="s" s="9">
+        <v>292</v>
+      </c>
+      <c r="B393" t="s" s="9">
+        <v>293</v>
+      </c>
+      <c r="C393" t="s" s="10">
+        <v>294</v>
+      </c>
+      <c r="D393" s="11">
+        <v>46271</v>
+      </c>
+      <c r="E393" s="12">
+        <v>46271</v>
+      </c>
+      <c r="F393" t="s" s="13">
         <v>585</v>
       </c>
     </row>

--- a/data/trips_verbose.xlsx
+++ b/data/trips_verbose.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="616">
   <si>
     <t>trips_verbose_v2</t>
   </si>
@@ -1768,9 +1768,6 @@
     <t>51.2230° N, 6.7825° E</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>Nice</t>
   </si>
   <si>
@@ -1804,6 +1801,12 @@
     <t>31.0470° N, 7.1319° W</t>
   </si>
   <si>
+    <t>Marrakesh</t>
+  </si>
+  <si>
+    <t>31.6225° N, 7.9898° W</t>
+  </si>
+  <si>
     <t>Casablanca</t>
   </si>
   <si>
@@ -1816,12 +1819,6 @@
     <t>34.0084° N, 6.8539° W</t>
   </si>
   <si>
-    <t>Marrakesh</t>
-  </si>
-  <si>
-    <t>31.6225° N, 7.9898° W</t>
-  </si>
-  <si>
     <t>Meknes</t>
   </si>
   <si>
@@ -1834,16 +1831,16 @@
     <t>34.0181° N, 5.0078° W</t>
   </si>
   <si>
+    <t>Chefchaouen</t>
+  </si>
+  <si>
+    <t>35.1688° N, 5.2684° W</t>
+  </si>
+  <si>
     <t>Tetouan</t>
   </si>
   <si>
     <t>35.5717° N, 5.3597° W</t>
-  </si>
-  <si>
-    <t>Chefchaouen</t>
-  </si>
-  <si>
-    <t>35.1688° N, 5.2684° W</t>
   </si>
   <si>
     <t>Tangier</t>
@@ -9898,19 +9895,17 @@
       <c r="E374" s="12">
         <v>46225</v>
       </c>
-      <c r="F374" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F374" s="14"/>
     </row>
     <row r="375" ht="20.05" customHeight="1">
       <c r="A375" t="s" s="9">
         <v>460</v>
       </c>
       <c r="B375" t="s" s="9">
+        <v>585</v>
+      </c>
+      <c r="C375" t="s" s="10">
         <v>586</v>
-      </c>
-      <c r="C375" t="s" s="10">
-        <v>587</v>
       </c>
       <c r="D375" s="11">
         <v>46225</v>
@@ -9918,19 +9913,17 @@
       <c r="E375" s="12">
         <v>46225</v>
       </c>
-      <c r="F375" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F375" s="14"/>
     </row>
     <row r="376" ht="20.05" customHeight="1">
       <c r="A376" t="s" s="9">
+        <v>587</v>
+      </c>
+      <c r="B376" t="s" s="9">
+        <v>587</v>
+      </c>
+      <c r="C376" t="s" s="10">
         <v>588</v>
-      </c>
-      <c r="B376" t="s" s="9">
-        <v>588</v>
-      </c>
-      <c r="C376" t="s" s="10">
-        <v>589</v>
       </c>
       <c r="D376" s="11">
         <v>46225</v>
@@ -9938,19 +9931,17 @@
       <c r="E376" s="12">
         <v>46225</v>
       </c>
-      <c r="F376" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F376" s="14"/>
     </row>
     <row r="377" ht="20.05" customHeight="1">
       <c r="A377" t="s" s="9">
         <v>460</v>
       </c>
       <c r="B377" t="s" s="9">
+        <v>585</v>
+      </c>
+      <c r="C377" t="s" s="10">
         <v>586</v>
-      </c>
-      <c r="C377" t="s" s="10">
-        <v>587</v>
       </c>
       <c r="D377" s="11">
         <v>46225</v>
@@ -9958,19 +9949,17 @@
       <c r="E377" s="12">
         <v>46226</v>
       </c>
-      <c r="F377" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F377" s="14"/>
     </row>
     <row r="378" ht="20.05" customHeight="1">
       <c r="A378" t="s" s="9">
         <v>460</v>
       </c>
       <c r="B378" t="s" s="9">
+        <v>589</v>
+      </c>
+      <c r="C378" t="s" s="10">
         <v>590</v>
-      </c>
-      <c r="C378" t="s" s="10">
-        <v>591</v>
       </c>
       <c r="D378" s="11">
         <v>46226</v>
@@ -9978,19 +9967,17 @@
       <c r="E378" s="12">
         <v>46227</v>
       </c>
-      <c r="F378" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F378" s="14"/>
     </row>
     <row r="379" ht="20.05" customHeight="1">
       <c r="A379" t="s" s="9">
+        <v>591</v>
+      </c>
+      <c r="B379" t="s" s="9">
         <v>592</v>
       </c>
-      <c r="B379" t="s" s="9">
+      <c r="C379" t="s" s="10">
         <v>593</v>
-      </c>
-      <c r="C379" t="s" s="10">
-        <v>594</v>
       </c>
       <c r="D379" s="11">
         <v>46227</v>
@@ -9998,19 +9985,17 @@
       <c r="E379" s="12">
         <v>46228</v>
       </c>
-      <c r="F379" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F379" s="14"/>
     </row>
     <row r="380" ht="20.05" customHeight="1">
       <c r="A380" t="s" s="9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B380" t="s" s="9">
+        <v>594</v>
+      </c>
+      <c r="C380" t="s" s="10">
         <v>595</v>
-      </c>
-      <c r="C380" t="s" s="10">
-        <v>596</v>
       </c>
       <c r="D380" s="11">
         <v>46228</v>
@@ -10018,139 +10003,125 @@
       <c r="E380" s="12">
         <v>46229</v>
       </c>
-      <c r="F380" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F380" s="14"/>
     </row>
     <row r="381" ht="20.05" customHeight="1">
       <c r="A381" t="s" s="9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B381" t="s" s="9">
+        <v>596</v>
+      </c>
+      <c r="C381" t="s" s="10">
         <v>597</v>
-      </c>
-      <c r="C381" t="s" s="10">
-        <v>598</v>
       </c>
       <c r="D381" s="11">
         <v>46229</v>
       </c>
       <c r="E381" s="12">
-        <v>46241</v>
-      </c>
-      <c r="F381" t="s" s="13">
-        <v>585</v>
-      </c>
+        <v>46236</v>
+      </c>
+      <c r="F381" s="14"/>
     </row>
     <row r="382" ht="20.05" customHeight="1">
       <c r="A382" t="s" s="9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B382" t="s" s="9">
+        <v>598</v>
+      </c>
+      <c r="C382" t="s" s="10">
         <v>599</v>
       </c>
-      <c r="C382" t="s" s="10">
-        <v>600</v>
-      </c>
       <c r="D382" s="11">
-        <v>46241</v>
+        <v>46236</v>
       </c>
       <c r="E382" s="12">
-        <v>46243</v>
-      </c>
-      <c r="F382" t="s" s="13">
-        <v>585</v>
-      </c>
+        <v>46249</v>
+      </c>
+      <c r="F382" s="14"/>
     </row>
     <row r="383" ht="20.05" customHeight="1">
       <c r="A383" t="s" s="9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B383" t="s" s="9">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C383" t="s" s="10">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D383" s="11">
-        <v>46243</v>
+        <v>46249</v>
       </c>
       <c r="E383" s="12">
-        <v>46248</v>
-      </c>
-      <c r="F383" t="s" s="13">
-        <v>585</v>
-      </c>
+        <v>46250</v>
+      </c>
+      <c r="F383" s="14"/>
     </row>
     <row r="384" ht="20.05" customHeight="1">
       <c r="A384" t="s" s="9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B384" t="s" s="9">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C384" t="s" s="10">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D384" s="11">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="E384" s="12">
-        <v>46250</v>
-      </c>
-      <c r="F384" t="s" s="13">
-        <v>585</v>
-      </c>
+        <v>46255</v>
+      </c>
+      <c r="F384" s="14"/>
     </row>
     <row r="385" ht="20.05" customHeight="1">
       <c r="A385" t="s" s="9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B385" t="s" s="9">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C385" t="s" s="10">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D385" s="11">
-        <v>46250</v>
+        <v>46255</v>
       </c>
       <c r="E385" s="12">
-        <v>46263</v>
-      </c>
-      <c r="F385" t="s" s="13">
-        <v>585</v>
-      </c>
+        <v>46257</v>
+      </c>
+      <c r="F385" s="14"/>
     </row>
     <row r="386" ht="20.05" customHeight="1">
       <c r="A386" t="s" s="9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B386" t="s" s="9">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C386" t="s" s="10">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D386" s="11">
-        <v>46263</v>
+        <v>46257</v>
       </c>
       <c r="E386" s="12">
         <v>46264</v>
       </c>
-      <c r="F386" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F386" s="14"/>
     </row>
     <row r="387" ht="20.05" customHeight="1">
       <c r="A387" t="s" s="9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B387" t="s" s="9">
+        <v>604</v>
+      </c>
+      <c r="C387" t="s" s="10">
         <v>605</v>
-      </c>
-      <c r="C387" t="s" s="10">
-        <v>606</v>
       </c>
       <c r="D387" s="11">
         <v>46264</v>
@@ -10158,19 +10129,17 @@
       <c r="E387" s="12">
         <v>46265</v>
       </c>
-      <c r="F387" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F387" s="14"/>
     </row>
     <row r="388" ht="20.05" customHeight="1">
       <c r="A388" t="s" s="9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B388" t="s" s="9">
+        <v>606</v>
+      </c>
+      <c r="C388" t="s" s="10">
         <v>607</v>
-      </c>
-      <c r="C388" t="s" s="10">
-        <v>608</v>
       </c>
       <c r="D388" s="11">
         <v>46265</v>
@@ -10178,19 +10147,17 @@
       <c r="E388" s="12">
         <v>46266</v>
       </c>
-      <c r="F388" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F388" s="14"/>
     </row>
     <row r="389" ht="20.05" customHeight="1">
       <c r="A389" t="s" s="9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B389" t="s" s="9">
+        <v>608</v>
+      </c>
+      <c r="C389" t="s" s="10">
         <v>609</v>
-      </c>
-      <c r="C389" t="s" s="10">
-        <v>610</v>
       </c>
       <c r="D389" s="11">
         <v>46266</v>
@@ -10198,19 +10165,17 @@
       <c r="E389" s="12">
         <v>46267</v>
       </c>
-      <c r="F389" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F389" s="14"/>
     </row>
     <row r="390" ht="20.05" customHeight="1">
       <c r="A390" t="s" s="9">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B390" t="s" s="9">
+        <v>610</v>
+      </c>
+      <c r="C390" t="s" s="10">
         <v>611</v>
-      </c>
-      <c r="C390" t="s" s="10">
-        <v>612</v>
       </c>
       <c r="D390" s="11">
         <v>46267</v>
@@ -10218,19 +10183,17 @@
       <c r="E390" s="12">
         <v>46268</v>
       </c>
-      <c r="F390" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F390" s="14"/>
     </row>
     <row r="391" ht="20.05" customHeight="1">
       <c r="A391" t="s" s="9">
         <v>502</v>
       </c>
       <c r="B391" t="s" s="9">
+        <v>612</v>
+      </c>
+      <c r="C391" t="s" s="10">
         <v>613</v>
-      </c>
-      <c r="C391" t="s" s="10">
-        <v>614</v>
       </c>
       <c r="D391" s="11">
         <v>46268</v>
@@ -10238,19 +10201,17 @@
       <c r="E391" s="12">
         <v>46269</v>
       </c>
-      <c r="F391" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F391" s="14"/>
     </row>
     <row r="392" ht="20.05" customHeight="1">
       <c r="A392" t="s" s="9">
         <v>502</v>
       </c>
       <c r="B392" t="s" s="9">
+        <v>614</v>
+      </c>
+      <c r="C392" t="s" s="10">
         <v>615</v>
-      </c>
-      <c r="C392" t="s" s="10">
-        <v>616</v>
       </c>
       <c r="D392" s="11">
         <v>46269</v>
@@ -10258,9 +10219,7 @@
       <c r="E392" s="12">
         <v>46271</v>
       </c>
-      <c r="F392" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F392" s="14"/>
     </row>
     <row r="393" ht="20.05" customHeight="1">
       <c r="A393" t="s" s="9">
@@ -10278,9 +10237,7 @@
       <c r="E393" s="12">
         <v>46271</v>
       </c>
-      <c r="F393" t="s" s="13">
-        <v>585</v>
-      </c>
+      <c r="F393" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
